--- a/data/STFM.xlsx
+++ b/data/STFM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\klimk\Documents\Gosy\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\klimk\Documents\Gosy\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E74259-EE28-4FB3-BD1E-BCE8A6F9008D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{858DF287-6D00-4E62-AB46-F878D09E63B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6270" yWindow="3720" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2400" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Вопросы" sheetId="1" r:id="rId1"/>
@@ -19,22 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Вопросы!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="864">
   <si>
     <t>Номер вопроса</t>
   </si>
@@ -967,12 +956,2552 @@
   <si>
     <t>Стратегический финансовый менеджмент</t>
   </si>
+  <si>
+    <t>Финансирование бизнеса</t>
+  </si>
+  <si>
+    <t>Главная цель финансовой модели</t>
+  </si>
+  <si>
+    <t>Просвирина Себестоим</t>
+  </si>
+  <si>
+    <t>Рассчитайте полную себестоимость изделия «Кольцо золотое», если прямые затраты на единицу изделия составили 16 тыс. руб., общие косвенные затраты компании распределяются исходя из ставки 1,4 руб. на 1 руб. прямых затрат.</t>
+  </si>
+  <si>
+    <t>Сметные (плановые) показатели: количество часов труда основных работников 8 500 тыс. руб., накладные расходы 148 750 тыс. руб. Фактические показатели: часы труда основных работников 7 928 тыс. руб., накладные расходы 146 200 тыс. руб. Определите, какова величина завышения или занижения распределенных накладных расходов.</t>
+  </si>
+  <si>
+    <t>занижены на 2550</t>
+  </si>
+  <si>
+    <t>завышены на 2550</t>
+  </si>
+  <si>
+    <t>завышены на 252</t>
+  </si>
+  <si>
+    <t>занижены на 7460</t>
+  </si>
+  <si>
+    <t>Рассчитайте полную себестоимость изделия Х (шасси для автомобиля) на основе следующих данных. Прямые затраты: материалы 9 тыс. руб., заработная плата 21 тыс. руб., прочие прямые затраты 4 тыс. руб. Время производства одного шасси составляет 6,5 час. Ставка распределения общепроизводственных расходов – 80 руб. на 1 мин. производственного времени.</t>
+  </si>
+  <si>
+    <t>Компания выпускает один вид продукции. Базой распределения косвенных расходов является выпуск продукции в шт. Плановый выпуск продукции за год составляет 180 000 ед. Плановые постоянные расходы составляют 4356000 руб. Определите ставку распределения накладных (постоянных) расходов.</t>
+  </si>
+  <si>
+    <t>Ставка распределения постоянных затрат составляет 950 руб. на 1 машино-час. работы оборудования. Плановое количество машино-часов составило 2000 час. в год при производственной программе 18000 шт. Найдите сумму занижения общепроизводственных накладных затрат при формировании прибыли отчетного периода, если фактические продажи составили 17300 шт.</t>
+  </si>
+  <si>
+    <t>Компания занимается производством газированной воды. Данная деятельность характеризуется высокой сезонностью: 60-70 процентов годовых продаж происходит в теплое время года. Если компания в управленческой отчетности использует калькулирование по переменным затратам, то в зимние месяцы (период низких продаж) при накоплении запаса к теплому времени года компания будет регистрировать</t>
+  </si>
+  <si>
+    <t>финансовый результат не будет зависеть от сезонности</t>
+  </si>
+  <si>
+    <t>вероятнее всего, прибыли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нет правильного ответа </t>
+  </si>
+  <si>
+    <t>вероятнее всего, убытки</t>
+  </si>
+  <si>
+    <t>Компания по производству приборов использует систему управления запасами «точно-в-срок» и поддерживает запасы на минимальном уровне. Как будет влиять на величину прибыли отчетного периода ситуация, когда фактический выпуск окажется ниже запланированного (при формировании полной себестоимости продукции):</t>
+  </si>
+  <si>
+    <t>значительное увеличение прибыли будет возникать, если только будет расти остаток готовой продукции</t>
+  </si>
+  <si>
+    <t>может иметь место сокращение прибыли в связи с ростом полной себестоимости единицы продукции</t>
+  </si>
+  <si>
+    <t>нет правильного ответа</t>
+  </si>
+  <si>
+    <t>значительного влияния на величину прибыли такая ситуация не оказывает</t>
+  </si>
+  <si>
+    <t>Компания использует распределение накладных расходов на основе ставки часа работы оборудования. Общезаводские сметные накладные расходы на год составляют 72000 тыс. руб., фактические — 73800 тыс. руб. За год компания распределила 71400 тыс. руб. расходов по 119 000 фактическим часам работы оборудования. Какое число часов работы оборудования за год заложено в смете</t>
+  </si>
+  <si>
+    <t>Компания распределяет накладные расходы по часам работы оборудования. Плановое количество часов работы оборудования установлено в размере 11 250, а сметные (плановые) накладные расходы — в размере 258 750 тыс. руб. Фактические показатели соответственно равны 10 980 час. и 254 692 тыс. руб. Таким образом, накладные расходы в учете:</t>
+  </si>
+  <si>
+    <t>завышены на 2152</t>
+  </si>
+  <si>
+    <t>завышены на 4058</t>
+  </si>
+  <si>
+    <t>занижены на 2152</t>
+  </si>
+  <si>
+    <t>занижены на 4058</t>
+  </si>
+  <si>
+    <t>Компания распределяет накладные расходы по часам труда основных работников. Сметные (плановые) показатели: количество часов труда основных работников 8 500 тыс. руб., накладные расходы 148 750 тыс. руб. Фактические показатели: часы труда основных работников 7 928 тыс. руб., накладные расходы 146 200 тыс. руб. Определите ставку накладных расходов на час труда основных работников.</t>
+  </si>
+  <si>
+    <t>Общие переменные затраты организации – 155200 руб., объем производства 400 ед. продукции. При объеме производства 450 ед. переменные затраты составят:</t>
+  </si>
+  <si>
+    <t>Просвирина операционный анализ</t>
+  </si>
+  <si>
+    <t>Нет верного ответа</t>
+  </si>
+  <si>
+    <t>Объем производства 300 ед. изделий, общие постоянные затраты организации – 13590 руб., общие переменные – 18600 руб. При объеме производства 450 ед. постоянные затраты будут следующими:</t>
+  </si>
+  <si>
+    <t>Известно, что при объеме производства в 350 шт. переменные затраты составили 65780 тыс. руб., постоянные затраты – 92340 тыс. руб. Рассчитайте величину общих затрат на единицу продукции при объеме в 480 шт.</t>
+  </si>
+  <si>
+    <t>Фактический объем продаж компании в 4 квартале составил 12 млн. руб., в том числе постоянные расходы 4 млн. руб. Средняя цена единицы продукции 300 руб., в том числе переменные расходы 200 руб. Производственные мощности загружены не полностью. Следует ли принять дополнительный заказ на продажу 500 шт. продукции по цене 210 руб.?</t>
+  </si>
+  <si>
+    <t>Заказ следует принять, так как предлагаемая цена выше переменных затрат</t>
+  </si>
+  <si>
+    <t>От заказа следует отказаться, так как предлагаемая цена ниже полной себестоимости продукции</t>
+  </si>
+  <si>
+    <t>От заказа следует отказаться, так как организация получит убыток</t>
+  </si>
+  <si>
+    <t>От заказа следует отказаться, так как цена продукции ниже цены, по которой организация продает свою продукцию</t>
+  </si>
+  <si>
+    <t>О компании известна следующая информация (в млн. руб. в год): выручка от продажи – 5,5; совокупные переменные затраты – 3,6 млн. руб.; постоянные затраты – 1,2 млн. руб. Определите силу воздействия операционного рычага (маржинальный доход/прибыль от продажи).</t>
+  </si>
+  <si>
+    <t>Цена продажи единицы продукции равна 200 руб., доля маржинального дохода в выручке составляет 0,6. Общая сумма постоянных расходов предприятия на прогнозируемый период составляют 120 тыс. руб. Рассчитайте критический объем продаж в прогнозном периоде (в рублях).(ответ цифрой)</t>
+  </si>
+  <si>
+    <t>Прогнозируемый объем продаж компании на следующий год составляет 600 млн. руб., в том числе постоянные расходы 264 млн. руб. Цена продажи 1 т продукции прогнозируется на уровне 40 тыс. руб., доля переменных расходов в цене составит 0,45. Рассчитайте прогнозируемый уровень запаса финансовой прочности компании в процентах. (ответ цифрой)</t>
+  </si>
+  <si>
+    <t>Найдите величину переменных затрат (в расчете на 1 л) на содержание автомобиля с пробегом 96000 км, если известно, что техническое обслуживание в год составляет 1200 тыс. руб., запасные части - 4000 руб. на 1600 км, бензин - 0,15 л на 1 км при цене за 1 л 50 руб., ежегодные платежи страховой компании - 40 тыс. руб.</t>
+  </si>
+  <si>
+    <t>Известны следующие данные за отчетный период, млн. руб.: выручка от продажи – 30; переменные расходы – 21; постоянные расходы – 6. Рассчитайте величину прибыли от продажи при снижении выручки в прогнозном периоде на 15 %</t>
+  </si>
+  <si>
+    <t>Общие переменные затраты организации составили в прошлом отчетном периоде 340000 тыс.руб., объем производства 500 ед. продукции, цена единицы продукции 980 тыс. руб. На следующий период ожидается объем производства 450 ед.; при этом удельные переменные затраты повышаются на 1%, поскольку не выполняется условие для получения от поставщиков скидки за объем. Найдите общую сумму маржинального дохода в планируемом периоде в тыс. руб.</t>
+  </si>
+  <si>
+    <t>Просвирина контролинг теория</t>
+  </si>
+  <si>
+    <t>В интересах менеджеров</t>
+  </si>
+  <si>
+    <t>все ответы верны</t>
+  </si>
+  <si>
+    <t>инициировать крупные инвестиционные проекты</t>
+  </si>
+  <si>
+    <t>увеличивать долю от прибыли в составе своего вознаграждения</t>
+  </si>
+  <si>
+    <t>увеличивать текущие прибыли</t>
+  </si>
+  <si>
+    <t>повышать собственную репутацию</t>
+  </si>
+  <si>
+    <t>Альтернативные затраты – это</t>
+  </si>
+  <si>
+    <t>затраты отвергнутых возможностей</t>
+  </si>
+  <si>
+    <t>вмененные издержки</t>
+  </si>
+  <si>
+    <t>упущенная выгода</t>
+  </si>
+  <si>
+    <t>Выберите правильное утверждение</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> собственный капитал является бесплатным источником финансирования деятельности компании</t>
+  </si>
+  <si>
+    <t>стоимость собственного капитала определяется акционерами</t>
+  </si>
+  <si>
+    <t>затраты на привлечение собственного капитала определяются альтернативными издержками</t>
+  </si>
+  <si>
+    <t>затраты компании на привлечение собственного капитала определяются суммой выплаченных дивидендов</t>
+  </si>
+  <si>
+    <t>Для какой отчетности справедливо требование обеспечения достоверности, осторожности и консерватизма</t>
+  </si>
+  <si>
+    <t>интегрированной отчетности</t>
+  </si>
+  <si>
+    <t>бухгалтерской (управленческой) отчетности</t>
+  </si>
+  <si>
+    <t>отчетности об интеллектуальном капитале компании</t>
+  </si>
+  <si>
+    <t>бухгалтерской (финансовой) отчетности</t>
+  </si>
+  <si>
+    <t>Почему службе снабжения выгодно увеличивать отсрочку платежа поставщикам</t>
+  </si>
+  <si>
+    <t>так можно сократить длительность финансового цикла компании (от денег до денег)</t>
+  </si>
+  <si>
+    <t>можно купить сырье и материалы со скидкой</t>
+  </si>
+  <si>
+    <t>так можно быстрее найти необходимые позиции для снабжения компании необходимыми материалами и комплектующим</t>
+  </si>
+  <si>
+    <t>Какая служба в компаниях в наибольшей степени заинтересована в сокращении просроченной дебиторской задолженности?</t>
+  </si>
+  <si>
+    <t>финансовая служба и организация в целом</t>
+  </si>
+  <si>
+    <t>служба управления персоналом</t>
+  </si>
+  <si>
+    <t>производственные подразделения</t>
+  </si>
+  <si>
+    <t>отдел маркетинга</t>
+  </si>
+  <si>
+    <t>Для какой категории пользователей создается информация о состоянии бизнеса в целом</t>
+  </si>
+  <si>
+    <t>для инвесторов и других внешних пользователе</t>
+  </si>
+  <si>
+    <t>для руководителей различных функциональных служб (снабжения, сбыта, производства, финансов, продаж)</t>
+  </si>
+  <si>
+    <t>для исполнительного органа (директора, управляющего</t>
+  </si>
+  <si>
+    <t>d. для всех работников предприятия</t>
+  </si>
+  <si>
+    <t>Причинами агентского конфликта являются</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> нарушение контракта со стороны агента</t>
+  </si>
+  <si>
+    <t>стремление собственника к получению наибольшего дохода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">все ответы верны </t>
+  </si>
+  <si>
+    <t>противоречие экономических интересов агента (менеджера) и принципала (собственника)</t>
+  </si>
+  <si>
+    <t>неполная информация о действиях агента (менеджера</t>
+  </si>
+  <si>
+    <t>Инсайдеры компании – это (выберите один правильный ответ)</t>
+  </si>
+  <si>
+    <t>акционеры компании</t>
+  </si>
+  <si>
+    <t>лица, имеющие доступ к внутренней информации о компании</t>
+  </si>
+  <si>
+    <t>. все сотрудники компании</t>
+  </si>
+  <si>
+    <t>топ-менеджеры компании</t>
+  </si>
+  <si>
+    <t>представители собственников в составе ревизионной комиссии</t>
+  </si>
+  <si>
+    <t>Каким подразделениям выгодно увеличивать отсрочки платежа клиентам</t>
+  </si>
+  <si>
+    <t>отделу капитального строительства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">службе снабжения </t>
+  </si>
+  <si>
+    <t>финансовой службе и организации в целом</t>
+  </si>
+  <si>
+    <t>производственным подразделениям</t>
+  </si>
+  <si>
+    <t>службе продаж</t>
+  </si>
+  <si>
+    <t>При росте обязательств, величина чистых активов будет…</t>
+  </si>
+  <si>
+    <t>увеличиваться</t>
+  </si>
+  <si>
+    <t>уменьшаться</t>
+  </si>
+  <si>
+    <t>не изменится</t>
+  </si>
+  <si>
+    <t>Выделите основные положения современной концепции фирмы с точки зрения агентской проблемы</t>
+  </si>
+  <si>
+    <t>фирма – это нерыночная структура, которая основана на иерархической системе управления и подчинении,</t>
+  </si>
+  <si>
+    <t>фирма – это уникальная совокупность материальных, нематериальных и человеческих ресурсов</t>
+  </si>
+  <si>
+    <t>фирма – неполный контракт между собственником и менеджером</t>
+  </si>
+  <si>
+    <t>Выберите ключевую (уникальную) функцию контроллинга</t>
+  </si>
+  <si>
+    <t>проведение экономического анализа и интерпретация показателей</t>
+  </si>
+  <si>
+    <t>координация деятельности подразделений компании</t>
+  </si>
+  <si>
+    <t>выявление резервов повышения эффективности деятельности компании</t>
+  </si>
+  <si>
+    <t>Выделите основные положения современной концепции фирмы по Р. Коузу</t>
+  </si>
+  <si>
+    <t>фирма – это нерыночная структура, которая основана на иерархической системе управления и власти,</t>
+  </si>
+  <si>
+    <t>Прямые затраты на продукцию</t>
+  </si>
+  <si>
+    <t>Непосредственно связаны с изготовлением продукции</t>
+  </si>
+  <si>
+    <t>Непосредственно связаны с осуществлением производственной деятельности</t>
+  </si>
+  <si>
+    <t>В момент возникновения можно непосредственно отнести на объект калькулирования на основе первичных документов</t>
+  </si>
+  <si>
+    <t>Изменяют свою величину в зависимости от уровня деловой активности организации</t>
+  </si>
+  <si>
+    <t>Если снижается доля постоянных затрат в выручке, это можно рассматривать как нормальную ситуацию в следующих условиях</t>
+  </si>
+  <si>
+    <t>растут объемы производства и продаж</t>
+  </si>
+  <si>
+    <t>повышается выручка за счет роста цен на продукцию компании</t>
+  </si>
+  <si>
+    <t>проявляются результаты политики сдерживания административных расходов</t>
+  </si>
+  <si>
+    <t>Какую методологию обязаны применять компании при построении современного управленческого учета</t>
+  </si>
+  <si>
+    <t>калькулирование полных затрат</t>
+  </si>
+  <si>
+    <t>может быть применена любая методология в зависимости от специфики бизнеса</t>
+  </si>
+  <si>
+    <t>калькулирование прямых затрат (директ-костинг)</t>
+  </si>
+  <si>
+    <t>калькулирование переменных затрат</t>
+  </si>
+  <si>
+    <t>Доля переменных затрат в выручке при росте выручки</t>
+  </si>
+  <si>
+    <t>не изменяется</t>
+  </si>
+  <si>
+    <t>снижается</t>
+  </si>
+  <si>
+    <t>растет</t>
+  </si>
+  <si>
+    <t>не зависит от выручки</t>
+  </si>
+  <si>
+    <t>Выделите основные положения современной концепции фирмы с точки зрения современной концепции фирмы по Р. Гранту</t>
+  </si>
+  <si>
+    <t>с</t>
+  </si>
+  <si>
+    <t>При росте объемов производства полная себестоимость единицы продукции</t>
+  </si>
+  <si>
+    <t>это зависит от масштаба производства</t>
+  </si>
+  <si>
+    <t>увеличивается</t>
+  </si>
+  <si>
+    <t>уменьшается</t>
+  </si>
+  <si>
+    <t>При росте объемов производства себестоимость единицы продукции по переменным затратам</t>
+  </si>
+  <si>
+    <t>Есть ли обязанность собственника передать полномочия текущего управления наёмному менеджеру?</t>
+  </si>
+  <si>
+    <t>Да есть по закону</t>
+  </si>
+  <si>
+    <t>Да, но в законе не закреплено</t>
+  </si>
+  <si>
+    <t>Нет, необходимости</t>
+  </si>
+  <si>
+    <t>По матрице BCG наиболее подходящая стратегия для компании относящейся к "дойной корове "</t>
+  </si>
+  <si>
+    <t>Вкладывать в поиск конкурентных преимуществ!</t>
+  </si>
+  <si>
+    <t>Реинвестировать прибыль!</t>
+  </si>
+  <si>
+    <t>Уходить с рынка, инвестировать в другой бизнес!</t>
+  </si>
+  <si>
+    <t>По матрице BCG наиболее подходящая стратегия для компании относящейся к "звезде"</t>
+  </si>
+  <si>
+    <t>Выплачивать дивиденды!</t>
+  </si>
+  <si>
+    <t>В структуре капитала компании 50 % составляют обязательства перед банками по средней контрактной ставке 10 %, Альтернативная ставка доходности собственного капитала (по данным финансового директора) 21 %. Величина активов 1200 млн. руб. Какова величина EVA, если чистая бухгалтерская прибыль составляет 250 млн. руб.? В ответе представлены значения в млн. руб.</t>
+  </si>
+  <si>
+    <t>Просвирина контролинг задачи новые</t>
+  </si>
+  <si>
+    <t>Чистая прибыль компании за отчетный год по годовой управленческой отчетности составляет 850 млн. руб., активы компании 5200 млн. руб., доля собственного капитала 70 %. По оценкам финансистов, в данной компании ставка доходности собственного капитала, основанная на альтернативной доходности капитала в сопоставимом бизнесе, составляет 20%. Найдите годовую величину EVA, млн. руб. В ответе представьте один знак после запятой. (аналогично)
+Экономическая прибыль в момент принятия решения должна учитывать потерю предыдущего дохода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600 * 0,21  = 126
+250-126 = </t>
+  </si>
+  <si>
+    <t>5200*0,75200*0.7 = 3640
+3640*0.2=728
+850-728 = 122</t>
+  </si>
+  <si>
+    <t>Высококвалифицированный специалист в области программирования планирует весь накопленный капитал вложить в собственный бизнес. В настоящее время его чистый совокупный доход (заработная плата плюс доходы по депозитам) составляет 200 тыс. руб. в месяц. Прогнозируемые показатели будущей компании (в год): выручка 5 млн руб., переменные затраты – 35 % от выручки, постоянные затраты – 2 млн. руб. Налогообложение – 6 % от выручки. Какова годовая экономическая прибыль от организации нового бизнеса?</t>
+  </si>
+  <si>
+    <t>200*12 = 2400
+5000-5000*0,35-2000-1750 - = 1250 - 0,06*5000
+-2400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высококвалифицированный специалист организует консалтинговый бизнес после длительной работы наемным работником с годовой заработной платой в 3 млн. руб. (после вычета НДФЛ). Прогнозируемая величина предпринимательского дохода (доходы за вычетом явных расходов) нового ИП составит 7000 тыс. руб. Необходимые основные средства (автомобиль, компьютеры, помещение) с общей рыночной стоимостью 8 000 тыс. руб. сейчас сдаются в аренду с годовым доходом после налогообложения 1000 тыс. руб. Рассчитайте прогнозируемую экономическую прибыль ИП с налогообложением 15 % от доходов за вычетом расходов. </t>
+  </si>
+  <si>
+    <t>7000-3000-1000-(7000*0,15)</t>
+  </si>
+  <si>
+    <t>Бизнес-единица генерирует годовую выручку в 4 млрд. руб., чистую прибыль 600 млн. руб., чистые активы составляют 3800 млн. руб., в том числе нераспределенная прибыль прошлого года 700 млн. руб. Рассчитайте среднюю отдачу на собственный капитал, в %, с одним знаком после запятой.</t>
+  </si>
+  <si>
+    <t>На начало 3100 на конец 3800
+600/(3100+3800)/2</t>
+  </si>
+  <si>
+    <t>Производственное предприятие рассматривает проект расширения бизнеса путем приобретения дополнительного автомобиля для внутризаводских перевозок. При этом на 0,2 млн. руб. увеличится годовая амортизация, на 1 млн. руб. в год сократятся затраты на ремонт и обслуживание автомобилей. Рассчитайте годовой операционный денежный поток проекта. Ставку налога на прибыль учитывайте (если необходимо) в размере 25%.</t>
+  </si>
+  <si>
+    <t>1-0,2 = 0,8*0,75 = 0,6 прибыль увел на 0,6
+0,2 налог
+Посмотреть на сколько увеличивается ЧП и прибавить амортизацию
+0,6+0,2 =0,8</t>
+  </si>
+  <si>
+    <t>а</t>
+  </si>
+  <si>
+    <t>Компания производит комплектующие А и Б. Известны следующие данные (за год). Количество машино-часов работы оборудования в цехе составляет 2 400 (1000 час. на прод. А и 1400 маш-час. на прод. Б). Общецеховые расходы составляют 82 млн. руб. Расходы вспомогательных производств (электроэнергия и ремонт оборудования) составляют 30 млн. руб. Определите величину косвенных затрат, приходящуюся на себестоимость каждой детали, в млн. руб. База распределения – машино-часы. За данный период реализована вся продукция.</t>
+  </si>
+  <si>
+    <t>82+30 = 112 косф затраты
+112/2400 = 0,0466
+0,0466*1000 = 46,6 А  
+0,0466*1400 = 65,33 – Б
+Будет база в виде прямых затрат</t>
+  </si>
+  <si>
+    <t>46,6 65,33</t>
+  </si>
+  <si>
+    <t>40,66 65,33</t>
+  </si>
+  <si>
+    <t>49,66 60,44</t>
+  </si>
+  <si>
+    <t>51,54 68,55</t>
+  </si>
+  <si>
+    <t>Рассчитайте годовой операционный денежный поток от проекта открытия новой сетевой кофейни, если необходимо инвестировать в ремонт помещения и оснащение кофейни 4 млн. руб. (период амортизации – 5 лет), поступления от продажи (данные за месяц) прогнозируются на уровне 2,9 млн. руб., переменные затраты – 900 тыс. руб., постоянные административные затраты компании возрастут на 880 тыс. руб. Расходы на консультантов для выбора места для размещения новой кофейни и проведение маркетинговых расчетов составили 220 тыс. руб. Ставку налога на прибыль учитывайте в размере 25%.</t>
+  </si>
+  <si>
+    <t>0.8 аморт
+2,9*12-0,9*12-0,88-0,8 = 22,32
+22,32 * 0,75 = 16,74 
+16,74+0,8 = 17,54</t>
+  </si>
+  <si>
+    <t>Компания открывает новый сетевой магазин. Инвестиции составят 10 млн. руб., период амортизации 5 лет. Чистая прибыль от продаж прогнозируется на уровне 85 млн. в год. При этом маржинальная прибыль в близлежащем магазине этой сети снизится на 12 млн. руб. за счет перераспределения потока клиентов. Рассчитайте прирост операционного денежного потока всей компании после реализации проекта. Ставка налога на прибыль 25 %.</t>
+  </si>
+  <si>
+    <t>Эффект для компании учитываем снижение маржинального дохода 
+12 снижение чистой прибыли сети уменьшение налоговой бвзы
+85 – 12*0,75 = 85-9 = 76
+10/5 = 2 + амортизация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компания реализует проект замены оборудования для энергоснабжения цехов основного производства. Инвестиции составят 20 млн. руб. Экономический эффект планируется получить за счет снижения энергопотерь (1 млн. руб. в год) и среднегодовых затрат на ремонт энергооборудования (5 млн. руб.). Рассчитайте прирост чистой прибыли от проекта (в млн. руб.). </t>
+  </si>
+  <si>
+    <t>6 млн сокращение затрат 
+6*0,75 = 4,5
+20 млн не учитываем</t>
+  </si>
+  <si>
+    <t>Производственная компания начинает производство нового продукта в имеющемся помещении с нулевой рыночной стоимостью. Затраты на оборудование составят 100 млн. руб. (период амортизации 10 лет). Рассчитайте NPV проекта, если компания будет производить продукцию в объеме 140 млн. руб. в год, чистая прибыль от продажи 22 млн. руб. Ставка дисконтирования для таких проектов в компании составляет 10 %.</t>
+  </si>
+  <si>
+    <t>Период амортизации равен сроку жизни проекта
+32 10 лет
+Ставка одинаковая и поток одинаковый нужно посчитать сумму коэфов дисконтирования = 6,1446
+-100
++32*6,1446</t>
+  </si>
+  <si>
+    <t>Компания производит два вида продукции – пластиковые и деревянные ящики. За сентябрь 2020 г. изготовлено 300 ед. пластиковых ящиков и 250 ед. деревянных. Прямые затраты на производство пластиковых ящиков составили 225000 руб., на производство деревянных – 425000 руб. Сумма косвенных затрат – 230000 руб. Определите сумму косвенных затрат, которую бухгалтер спишет на себестоимость деревянных ящиков, если за базу распределения принять прямые затраты.</t>
+  </si>
+  <si>
+    <t>230000/650000*425000 косвенные / все * затраты на ящик</t>
+  </si>
+  <si>
+    <t>Рассчитайте ставку распределения общепроизводственных расходов на 1 машино-час, общую для всего предприятия. Известно, что общецеховые расходы цеха литья составляют 2 млн. руб., цеха сборки 5,6 млн. руб. Количество машиночасов работы оборудования составляет соответственно 2 400 и 40 000.</t>
+  </si>
+  <si>
+    <t>7,6/42400</t>
+  </si>
+  <si>
+    <t>. Рассчитайте величину производственной себестоимости выпуска, используя следующие данные (млн. руб.): стоимость материалов 9,0, топливо 60,0, амортизация оборудования 18,0, зарплата производственных рабочих 25,0, оплата сверхурочных 3,0, заработная плата инженерно-технических сотрудников цеха 4,0, управленческие расходы 1,5, реклама 2,5, транспортные расходы по доставке продукции клиентам 12,0. Ответ представьте целым числом в млн. руб.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стоимость материалов 9,0, топливо 60,0, амортизация оборудования 18,0, зарплата производственных рабочих 25,0, оплата сверхурочных 3,0, заработная плата инженерно-технических сотрудников цеха 4,0, </t>
+  </si>
+  <si>
+    <t>Может ли быть чистая прибыль предприятия больше, чем валовая прибыль?</t>
+  </si>
+  <si>
+    <t>да, чистая прибыль всегда выше валовой, так как для ее расчета необходимо к валовой прибыли прибавить коммерческие и управленческие расходы</t>
+  </si>
+  <si>
+    <t>да, в случае если предприятие основной доход получает по прочим видам деятельности</t>
+  </si>
+  <si>
+    <t>нет, так как чистая прибыль всегда меньше валовой прибыли на величину налога</t>
+  </si>
+  <si>
+    <t>Чем больше доля заемных средств в структуре пассивного капитала предприятия, ...</t>
+  </si>
+  <si>
+    <t>тем выше ликвидность баланса</t>
+  </si>
+  <si>
+    <t>тем ниже стоимость заемного капитала</t>
+  </si>
+  <si>
+    <t>тем выше финансовая устойчивость</t>
+  </si>
+  <si>
+    <t>тем ниже финансовая устойчивость</t>
+  </si>
+  <si>
+    <t>От скольких факторов в соответствии с моделью Дюпона зависит рентабельность собственного капитала?</t>
+  </si>
+  <si>
+    <t>от четырех</t>
+  </si>
+  <si>
+    <t>от трех</t>
+  </si>
+  <si>
+    <t>от двух</t>
+  </si>
+  <si>
+    <t>от одного</t>
+  </si>
+  <si>
+    <t>К долгосрочному заемному капиталу НЕ относится ...</t>
+  </si>
+  <si>
+    <t>эмиссия облигаций на 3 года</t>
+  </si>
+  <si>
+    <t>привлечение займа физического лица сроком на 2 года</t>
+  </si>
+  <si>
+    <t>оформление банковского кредита сроком на 15 месяцев</t>
+  </si>
+  <si>
+    <t>покупка облигаций на 3 года</t>
+  </si>
+  <si>
+    <t>В соответствии с моделью Дюпона от какого фактора зависит рентабельность активов?</t>
+  </si>
+  <si>
+    <t>от величины активов</t>
+  </si>
+  <si>
+    <t>от прибыли</t>
+  </si>
+  <si>
+    <t>от рентабельности продукции</t>
+  </si>
+  <si>
+    <t>от рентабельности продаж</t>
+  </si>
+  <si>
+    <t>Формой отчетности, в которой отражается информация о структуре активного капитала предприятия, является</t>
+  </si>
+  <si>
+    <t>отчет о движении денежных средств</t>
+  </si>
+  <si>
+    <t>бухгалтерский баланс</t>
+  </si>
+  <si>
+    <t>отчет о финансовых результатах</t>
+  </si>
+  <si>
+    <t>в основных формах отчетности не содержится информация об активном капитале </t>
+  </si>
+  <si>
+    <t>Использование собственного капитала для финансирования деятельности характеризуется</t>
+  </si>
+  <si>
+    <t>более высокой способностью генерировать прибыль, так как не нужно платить проценты за его использование</t>
+  </si>
+  <si>
+    <t>ростом рентабельности собственного капитала</t>
+  </si>
+  <si>
+    <t>возможностью в сжатые сроки нарастить масштаб деятельности</t>
+  </si>
+  <si>
+    <t>повышает риски неплатежеспособности</t>
+  </si>
+  <si>
+    <t>Отношения по поводу создания, распределения и использования фондов денежных средств - это...</t>
+  </si>
+  <si>
+    <t>бюджет</t>
+  </si>
+  <si>
+    <t>финансы</t>
+  </si>
+  <si>
+    <t>финансово-кредитная система</t>
+  </si>
+  <si>
+    <t>финансовая система</t>
+  </si>
+  <si>
+    <t>количество кредитов у такого предприятия сокращается</t>
+  </si>
+  <si>
+    <t>показатели не связаны между собой и никаких выводов сделать нельзя</t>
+  </si>
+  <si>
+    <t>эффективность деятельности предприятия падает в динамике</t>
+  </si>
+  <si>
+    <t>предприятие работает не эффективно</t>
+  </si>
+  <si>
+    <t>О чем свидетельствует то, что рентабельность активов предприятия ниже средневзвешенной стоимости его капитала?</t>
+  </si>
+  <si>
+    <t>Себестоимость</t>
+  </si>
+  <si>
+    <t>Прибыль до налогообложения</t>
+  </si>
+  <si>
+    <t>Прибыль после налогообложения</t>
+  </si>
+  <si>
+    <t>Суммы дивидендов к выплате по акциям уменьшают:</t>
+  </si>
+  <si>
+    <t>Проверить вручную</t>
+  </si>
+  <si>
+    <t>d. 60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. 46% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. 150% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. 400% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рассчитайте запас финансовой прочности, если компания продает 1000 шт. продукции при цене 13 000 руб., постоянные затраты составляют 2 400 000 руб., а удельные переменные - 7 000 руб. </t>
+  </si>
+  <si>
+    <t>d. 48%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. 30% </t>
+  </si>
+  <si>
+    <t>b. 3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a. 12% </t>
+  </si>
+  <si>
+    <t>Рентабельность продаж равна 12%, а коэффициент оборачиваемости активов 4, чему равна рентабельность активов?</t>
+  </si>
+  <si>
+    <t>d. тем выше финансовая устойчивость</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. тем ниже финансовая устойчивость </t>
+  </si>
+  <si>
+    <t>b. тем выше ликвидность баланса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. тем ниже стоимость заемного капитала </t>
+  </si>
+  <si>
+    <t>Чем больше доля заемных средств в структуре пассивного капитала предприятия, …</t>
+  </si>
+  <si>
+    <t>d. росте прибыли предприятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. сокращении деятельности предприятия </t>
+  </si>
+  <si>
+    <t>b. убыточной деятельности предприятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. расширении деятельности предприятия </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отрицательный чистый денежный поток по инвестиционной деятельности свидетельствует ... </t>
+  </si>
+  <si>
+    <t>d. это хорошо в ситуации падения продаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. это плохо в ситуации роста продаж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. это хорошо в ситуации роста продаж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В структуре затрат первого предприятия 90% составляют постоянные затраты, а в структуре затрат второго предприятия доля постоянных затрат равна 20%. Что можно сказать о структуре затрат первого предприятия в сравнении со вторым? Выберите один : </t>
+  </si>
+  <si>
+    <t>внеоборотные активы</t>
+  </si>
+  <si>
+    <t>обязательства предприятия</t>
+  </si>
+  <si>
+    <t>источники собственных средств</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уставный капитал, резервы, нераспределенная прибыль - это: </t>
+  </si>
+  <si>
+    <t>фонды и резервы</t>
+  </si>
+  <si>
+    <t>источники собственных и заемных средств</t>
+  </si>
+  <si>
+    <t>резервы, прибыль и ссуды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что отражается в пассиве баланса: </t>
+  </si>
+  <si>
+    <t>при реинвестировании чистой прибыли в деятельность компании</t>
+  </si>
+  <si>
+    <t>если предприятие является монополистом на рынке</t>
+  </si>
+  <si>
+    <t>при сокращении расходов на управленческий аппарат</t>
+  </si>
+  <si>
+    <t>при условии стабильных выплат дивидендов акционерам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Развитие и расширение деятельности в долгосрочной перспективе возможно только </t>
+  </si>
+  <si>
+    <t>d. денежный приток по финансовой деятельности</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. денежный приток по операционной деятельности </t>
+  </si>
+  <si>
+    <t>b. денежный приток по инвестиционной деятельности</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. денежный отток по инвестиционной деятельности </t>
+  </si>
+  <si>
+    <t>Выручка, полученная предприятием, влияет на …</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. 10 у.е</t>
+  </si>
+  <si>
+    <t>c. 60 у.е.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. 20 у.е. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. 55 у.е. </t>
+  </si>
+  <si>
+    <t>Оцените потребность в дополнительном финансировании, если предприятие не имело денег на начало периода, а чистые денежные потоки составили: по операционной деятельности 45 у.е., по инвестиционной  -60 у.е., по финансовой 5у.е.</t>
+  </si>
+  <si>
+    <t>Если дифференциал эффекта финансового рычага положительный, то какой источник финансирования выгоднее для предприятия? 8.10:</t>
+  </si>
+  <si>
+    <t>выпуск обыкновенных акций;</t>
+  </si>
+  <si>
+    <t>выпуск привилегированных акций;</t>
+  </si>
+  <si>
+    <t>банковский кредит</t>
+  </si>
+  <si>
+    <t>Вопрос 1
+Выполнен
+Баллов: 1,00 из 1,00
+Если дифференциал эффекта финансового рычага положительный, то какой источник финансирования выгоднее для
+предприятия? 8.10:
+Выберите один ответ:
+a.
+выпуск обыкновенных акций;
+b.
+выпуск привилегированных акций;
+c.
+банковский кредит.</t>
+  </si>
+  <si>
+    <t>Значение эффекта финансового рычага, рассчитанное по европейской концепции, составило 12%. Что это означает? 8.9:</t>
+  </si>
+  <si>
+    <t>в результате привлечения платного кредита рентабельность собственных средств возрастет на 12%</t>
+  </si>
+  <si>
+    <t>в результате кредитования объем продаж возрастет на 12%;</t>
+  </si>
+  <si>
+    <t>предприятие привлекает кредит под 12% годовых;</t>
+  </si>
+  <si>
+    <t>в результате кредитования оборачиваемость активов возрастет на 12%;</t>
+  </si>
+  <si>
+    <t>Вопрос 2
+Выполнен
+Баллов: 1,00 из 1,00
+Значение эффекта финансового рычага, рассчитанное по европейской концепции, составило 12%. Что это означает? 8.9:
+Выберите один ответ:
+a.
+в результате привлечения платного кредита рентабельность собственных средств возрастет на 12%.
+b.
+в результате кредитования объем продаж возрастет на 12%;
+c.
+предприятие привлекает кредит под 12% годовых;
+d.
+в результате кредитования оборачиваемость активов возрастет на 12%;</t>
+  </si>
+  <si>
+    <t>Проект, рассчитанный на 10 лет, требует инвестиций в размере 150 тыс. дол. В первые 5 лет никаких поступлений не ожидается, однако в последующие 5 лет ежегодный доход составит 50 тыс.долларов. Определите чистый дисконтированный доход (NPV) проекта, если ставка дисконтирования составляет 15%. 4.5 :</t>
+  </si>
+  <si>
+    <t>– 66670 ;</t>
+  </si>
+  <si>
+    <t>83330</t>
+  </si>
+  <si>
+    <t>100940;</t>
+  </si>
+  <si>
+    <t>Вопрос 3
+Выполнен
+Баллов: 1,00 из 1,00
+Проект, рассчитанный на 10 лет, требует инвестиций в размере 150 тыс. дол. В первые 5 лет никаких поступлений не
+ожидается, однако в последующие 5 лет ежегодный доход составит 50 тыс.долларов. Определите чистый
+дисконтированный доход (NPV) проекта, если ставка дисконтирования составляет 15%. 4.5 :
+Выберите один ответ:
+a.
+– 66670 ;
+b.
+83330.
+c.
+100940;</t>
+  </si>
+  <si>
+    <t>В каком из ниже перечисленных случаев увеличение эффекта финансового рычага способствует росту рентабельности собственного капитала? 8.11:</t>
+  </si>
+  <si>
+    <t>цена заемных средств равна рентабельности вложений капитала</t>
+  </si>
+  <si>
+    <t>цена заемных средств ниже рентабельности вложений капитала;</t>
+  </si>
+  <si>
+    <t>цена заемных средств выше рентабельности вложений капитала;</t>
+  </si>
+  <si>
+    <t>Вопрос 4
+Выполнен
+Баллов: 1,00 из 1,00
+В каком из ниже перечисленных случаев увеличение эффекта финансового рычага способствует росту рентабельности
+собственного капитала? 8.11:
+Выберите один ответ:
+a.
+цена заемных средств равна рентабельности вложений капитала.
+b.
+цена заемных средств ниже рентабельности вложений капитала;
+c.
+цена заемных средств выше рентабельности вложений капитала;</t>
+  </si>
+  <si>
+    <t>При разработке инвестиционной стратегии предприятие рассматривает вопрос о целесообразности инвестирования 150 ден. ед. в проект, который через 2 года принесет 200 ден. ед. Минимальная цена капитала 10%. Определите выгодность инвестиции с помощью показателя чистого дисконтированного дохода (NPV). 4.3 :</t>
+  </si>
+  <si>
+    <t>15,3 ден. ед</t>
+  </si>
+  <si>
+    <t>31,8 ден. ед.;</t>
+  </si>
+  <si>
+    <t>92 ден. ед.;</t>
+  </si>
+  <si>
+    <t>Вопрос 5
+Выполнен
+Баллов: 1,00 из 1,00
+При разработке инвестиционной стратегии предприятие рассматривает вопрос о целесообразности инвестирования 150
+ден. ед. в проект, который через 2 года принесет 200 ден. ед. Минимальная цена капитала 10%. Определите выгодность
+инвестиции с помощью показателя чистого дисконтированного дохода (NPV). 4.3 :
+Выберите один ответ:
+a.
+15,3 ден. ед.
+b.
+31,8 ден. ед.;
+c.
+92 ден. ед.;</t>
+  </si>
+  <si>
+    <t>Какая из фаз кризиса предприятия требует принятия экстренных мер? 10.7:</t>
+  </si>
+  <si>
+    <t>убыточность;</t>
+  </si>
+  <si>
+    <t>снижение рентабельности;</t>
+  </si>
+  <si>
+    <t>неплатежеспособность;</t>
+  </si>
+  <si>
+    <t>истощение резервов вплоть до полного исчезновения</t>
+  </si>
+  <si>
+    <t>Вопрос 6
+Выполнен
+Баллов: 1,00 из 1,00
+Какая из фаз кризиса предприятия требует принятия экстренных мер? 10.7:
+Выберите один ответ:
+a.
+убыточность;
+b.
+снижение рентабельности;
+c.
+неплатежеспособность;
+d.
+истощение резервов вплоть до полного исчезновения.</t>
+  </si>
+  <si>
+    <t>Что такое несистематический риск финансового актива / портфеля? 3.11 :</t>
+  </si>
+  <si>
+    <t>это риск, присущий конкретному активу и проистекающий из его внутренних особенностей;</t>
+  </si>
+  <si>
+    <t>это риск, связанный с изменением конъюнктуры финансового рынка под влиянием макроэкономических факторов;</t>
+  </si>
+  <si>
+    <t>это риск, возникающий время от времени в зависимости от тех или иных обстоятельств;</t>
+  </si>
+  <si>
+    <t>Вопрос 7
+Выполнен
+Баллов: 1,00 из 1,00
+Что такое несистематический риск финансового актива / портфеля? 3.11 :
+Выберите один ответ:
+a.
+это риск, присущий конкретному активу и проистекающий из его внутренних особенностей;
+b.
+это риск, связанный с изменением конъюнктуры финансового рынка под влиянием макроэкономических
+факторов;
+c.
+это риск, возникающий время от времени в зависимости от тех или иных обстоятельств;</t>
+  </si>
+  <si>
+    <t>Какой из ниже приведенных показателей определяется как отношение общей суммы средств, которую необходимо уплатить за использование определенного объема привлекаемых на рынке капитала финансовых ресурсов, к этому объему, выраженное в процентах к этому объему? 5.5 :</t>
+  </si>
+  <si>
+    <t>верного ответа нет. капитала</t>
+  </si>
+  <si>
+    <t>стоимость активов компании,</t>
+  </si>
+  <si>
+    <t>стоимость капитала,</t>
+  </si>
+  <si>
+    <t>предельная стоимость</t>
+  </si>
+  <si>
+    <t>Вопрос 8
+Выполнен
+Баллов: 1,00 из 1,00
+Какой из ниже приведенных показателей определяется как отношение общей суммы средств, которую необходимо
+уплатить за использование определенного объема привлекаемых на рынке капитала финансовых ресурсов, к этому
+объему, выраженное в процентах к этому объему? 5.5 :
+Выберите один ответ:
+a.
+верного ответа нет. капитала
+b.
+стоимость активов компании,
+c.
+стоимость капитала,
+d.
+предельная стоимость</t>
+  </si>
+  <si>
+    <t>Как называется стратегия, предусматривающая сворачивание бизнеса, в том числе продажа нерентабельно функционирующей деловой единицы? 10.4:</t>
+  </si>
+  <si>
+    <t>стратегия нестабильности;</t>
+  </si>
+  <si>
+    <t>стратегия сокращения;</t>
+  </si>
+  <si>
+    <t>стратегия роста;</t>
+  </si>
+  <si>
+    <t>функциональная стратегия</t>
+  </si>
+  <si>
+    <t>Вопрос 9
+Выполнен
+Баллов: 1,00 из 1,00
+Как называется стратегия, предусматривающая сворачивание бизнеса, в том числе продажа нерентабельно
+функционирующей деловой единицы? 10.4:
+Выберите один ответ:
+a.
+стратегия нестабильности;
+b.
+стратегия сокращения;
+c.
+стратегия роста;
+d.
+функциональная стратегия.</t>
+  </si>
+  <si>
+    <t>Активы компании А составляют 20 ден.ед., операционная прибыль - 4 ден.ед., налог на прибыль - 40%. Доля заемных средств -50%, выплаты по заемным средствам - 12 % годовых. Рассчитайте рентабельность собственного капитала компании А. 2.2 :</t>
+  </si>
+  <si>
+    <t>16,8%;</t>
+  </si>
+  <si>
+    <t>21,6%;</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Вопрос 10
+Выполнен
+Баллов: 1,00 из 1,00
+Активы компании А составляют 20 ден.ед., операционная прибыль - 4 ден.ед., налог на прибыль - 40%. Доля заемных
+средств -50%, выплаты по заемным средствам - 12 % годовых. Рассчитайте рентабельность собственного капитала
+компании А. 2.2 :
+Выберите один ответ:
+a.
+16,8%;
+b.
+21,6%;
+c.
+40%;
+d.
+24%.</t>
+  </si>
+  <si>
+    <t>Что такое финансовая стратегия предприятия? 1.1 :</t>
+  </si>
+  <si>
+    <t>это процесс формирования финансовых ресурсов предприятия;</t>
+  </si>
+  <si>
+    <t>это процесс использования финансовых ресурсов предприятия;</t>
+  </si>
+  <si>
+    <t>это совокупность целей и задач в сфере финансовой деятельности предприятия</t>
+  </si>
+  <si>
+    <t>Вопрос 11
+Выполнен
+Баллов: 1,00 из 1,00
+Что такое финансовая стратегия предприятия? 1.1 :
+Выберите один ответ:
+a.
+это процесс формирования финансовых ресурсов предприятия;
+b.
+это процесс использования финансовых ресурсов предприятия;
+c.
+это совокупность целей и задач в сфере финансовой деятельности предприятия.</t>
+  </si>
+  <si>
+    <t>К какому типу относится такая процедура банкротства как "финансовое оздоровление?" 10.8:</t>
+  </si>
+  <si>
+    <t>это судебная процедура</t>
+  </si>
+  <si>
+    <t>это внесудебная процедура;</t>
+  </si>
+  <si>
+    <t>Вопрос 12
+Выполнен
+Баллов: 1,00 из 1,00
+К какому типу относится такая процедура банкротства как "финансовое оздоровление?" 10.8:
+Выберите один ответ:
+a.
+это судебная процедура.
+b.
+это внесудебная процедура;</t>
+  </si>
+  <si>
+    <t>Рассчитать коэффициент маржинальной прибыли предприятия, если порог его рентабельности равен 2 млн. руб., сумма постоянных издержек составляет 3 млн. руб. за период. 9.4:</t>
+  </si>
+  <si>
+    <t>0,67;</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>6;</t>
+  </si>
+  <si>
+    <t>Вопрос 13
+Выполнен
+Баллов: 1,00 из 1,00
+Рассчитать коэффициент маржинальной прибыли предприятия, если порог его рентабельности равен 2 млн. руб., сумма
+постоянных издержек составляет 3 млн. руб. за период. 9.4:
+Выберите один ответ:
+a.
+0,67;
+b.
+1,5.
+c.
+6;
+d.
+информации для расчета недостаточно;</t>
+  </si>
+  <si>
+    <t>Инвестиционная стратегия предусматривает реализацию инвестиционного проекта. Рассчитайте ставку дисконтирования для этого проекта, если информация об источниках его финансирования приведена в следующей таблице. Название источника Доля источника, % Стоимость источника, % 1. Дополнительная эмиссия акций 40,0 20,0 2. Долгосрочные кредиты 35,0 12,0 3. Краткосрочные кредиты 25,0 14,0 Итого 100,0 – 4.1 :</t>
+  </si>
+  <si>
+    <t>15,3%;</t>
+  </si>
+  <si>
+    <t>0,153%;</t>
+  </si>
+  <si>
+    <t>0,157%</t>
+  </si>
+  <si>
+    <t>15,7%;</t>
+  </si>
+  <si>
+    <t>Вопрос 14
+Выполнен
+Баллов: 1,00 из 1,00
+Инвестиционная стратегия предусматривает реализацию инвестиционного проекта. Рассчитайте ставку
+дисконтирования для этого проекта, если информация об источниках его финансирования приведена в следующей
+таблице.
+Название источника
+Доля источника, %
+Стоимость источника,
+%
+1. Дополнительная эмиссия акций
+40,0
+20,0
+2. Долгосрочные кредиты
+35,0
+12,0
+3. Краткосрочные кредиты
+25,0
+14,0
+Итого
+100,0
+–
+4.1 :
+Выберите один ответ:
+a.
+15,3%;
+b.
+0,153%;
+c.
+0,157%.
+d.
+15,7%;</t>
+  </si>
+  <si>
+    <t>Компания производит программные продукты. Постоянные издержки отсутствуют. Годовой объем реализации составляет 1 млн. руб., переменные издержки составляют 80 % отпускной цены. Чему равно значение операционного рычага? 9.11:</t>
+  </si>
+  <si>
+    <t>1,0;</t>
+  </si>
+  <si>
+    <t>1,25;</t>
+  </si>
+  <si>
+    <t>5,0</t>
+  </si>
+  <si>
+    <t>Вопрос 15
+Выполнен
+Баллов: 1,00 из 1,00
+Компания производит программные продукты. Постоянные издержки отсутствуют. Годовой объем реализации
+составляет 1 млн. руб., переменные издержки составляют 80 % отпускной цены. Чему равно значение операционного
+рычага? 9.11:
+Выберите один ответ:
+a.
+информации для расчета недостаточно;
+b.
+1,0;
+c.
+1,25;
+d.
+5,0.</t>
+  </si>
+  <si>
+    <t>К чему стремится предприятия для повышения рентабельности собственного капитала? 8.6:</t>
+  </si>
+  <si>
+    <t>снизить плечо финансового рычага и снизить дифференциал финансового рычага;</t>
+  </si>
+  <si>
+    <t>снизить плечо финансового рычага и повысить дифференциал финансового рычага;</t>
+  </si>
+  <si>
+    <t>повысить плечо финансового рычага и снизить дифференциал финансового рычага;</t>
+  </si>
+  <si>
+    <t>повысить плечо финансового рычага и повысить дифференциал финансового рычага;</t>
+  </si>
+  <si>
+    <t>Вопрос 16
+Выполнен
+Баллов: 0,00 из 1,00
+К чему стремится предприятия для повышения рентабельности собственного капитала? 8.6:
+Выберите один ответ:
+a.
+снизить плечо финансового рычага и снизить дифференциал финансового рычага;
+b.
+снизить плечо финансового рычага и повысить дифференциал финансового рычага;
+c.
+повысить плечо финансового рычага и снизить дифференциал финансового рычага;
+d.
+повысить плечо финансового рычага и повысить дифференциал финансового рычага;</t>
+  </si>
+  <si>
+    <t>Рассчитайте величину цены капитала фирмы при следующих условиях: общая величина акционерного капитала  48 млн. руб., нераспределенная прибыль  1800 тыс. руб., долгосрочные обязательства  54 млн. руб. При этом доходность акций фирмы составляет 19%, цена нераспределенной прибыли составляет 34%, а средняя расчетная ставка по долгосрочным обязательствам равна 28%. В расчетах примите округление до сотых. 6.4:</t>
+  </si>
+  <si>
+    <t>23,98%;</t>
+  </si>
+  <si>
+    <t>27%;</t>
+  </si>
+  <si>
+    <t>23,3%</t>
+  </si>
+  <si>
+    <t>Вопрос 17
+Выполнен
+Баллов: 1,00 из 1,00
+Рассчитайте величину цены капитала фирмы при следующих условиях: общая величина акционерного капитала  48 млн.
+руб., нераспределенная прибыль  1800 тыс. руб., долгосрочные обязательства  54 млн. руб. При этом доходность акций
+фирмы составляет 19%, цена нераспределенной прибыли составляет 34%, а средняя расчетная ставка по долгосрочным
+обязательствам равна 28%. В расчетах примите округление до сотых. 6.4:
+Выберите один ответ:
+a.
+23,98%;
+b.
+27%;
+c.
+23,3%.</t>
+  </si>
+  <si>
+    <t>Закончите предложение: «Чем больше сила воздействия финансового рычага (по американской концепции), тем в большей степени…». 8.17:</t>
+  </si>
+  <si>
+    <t>возрастает риск потери или недополучения операционной прибыли;</t>
+  </si>
+  <si>
+    <t>возрастает риск невыплаты дивидендов акционерам;</t>
+  </si>
+  <si>
+    <t>возрастает риск непогашения процентов за кредита</t>
+  </si>
+  <si>
+    <t>Вопрос 18
+Выполнен
+Баллов: 0,00 из 1,00
+Закончите предложение: «Чем больше сила воздействия финансового рычага (по американской концепции), тем в
+большей степени…». 8.17:
+Выберите один ответ:
+a.
+возрастает риск потери или недополучения операционной прибыли;
+b.
+возрастает риск невыплаты дивидендов акционерам;
+c.
+все ответы верны.
+d.
+возрастает риск непогашения процентов за кредита</t>
+  </si>
+  <si>
+    <t>Повлияет ли повышение ставки дисконтирования на значение внутренней нормы доходности (IRR) проекта? 3.4 :</t>
+  </si>
+  <si>
+    <t>IRR может как сниться, так и увеличиться</t>
+  </si>
+  <si>
+    <t>да, IRR повысится;</t>
+  </si>
+  <si>
+    <t>да, IRR снизится;</t>
+  </si>
+  <si>
+    <t>нет, IRR не изменится;</t>
+  </si>
+  <si>
+    <t>Вопрос 19
+Выполнен
+Баллов: 1,00 из 1,00
+Повлияет ли повышение ставки дисконтирования на значение внутренней нормы доходности (IRR) проекта? 3.4 :
+Выберите один ответ:
+a.
+IRR может как сниться, так и увеличиться.
+b.
+да, IRR повысится;
+c.
+да, IRR снизится;
+d.
+нет, IRR не изменится;</t>
+  </si>
+  <si>
+    <t>Для какого из типов реструктуризации восстановление платежеспособности и поддержание уровня ликвидности является основной целью? 7.6:</t>
+  </si>
+  <si>
+    <t>для оперативного типа реструктуризации;</t>
+  </si>
+  <si>
+    <t>для инвестиционного типа реструктуризации</t>
+  </si>
+  <si>
+    <t>для стратегического типа реструктуризации;</t>
+  </si>
+  <si>
+    <t>Вопрос 20
+Выполнен
+Баллов: 1,00 из 1,00
+Для какого из типов реструктуризации восстановление платежеспособности и поддержание уровня ликвидности
+является основной целью? 7.6:
+Выберите один ответ:
+a.
+для оперативного типа реструктуризации;
+b.
+для инвестиционного типа реструктуризации.
+c.
+для стратегического типа реструктуризации;</t>
+  </si>
+  <si>
+    <t>От каких ниже перечисленных факторов НЕ зависят постоянные издержки производства? 8.2:</t>
+  </si>
+  <si>
+    <t>от объема и периода времени, в течении которого выпущена продукция;</t>
+  </si>
+  <si>
+    <t>от объема выпуска продукции</t>
+  </si>
+  <si>
+    <t>от объема и вида выпускаемой продукции;</t>
+  </si>
+  <si>
+    <t>Вопрос 21
+Выполнен
+Баллов: 1,00 из 1,00
+От каких ниже перечисленных факторов НЕ зависят постоянные издержки производства? 8.2:
+Выберите один ответ:
+a.
+от объема и периода времени, в течении которого выпущена продукция;
+b.
+от объема выпуска продукции.
+c.
+от объема и вида выпускаемой продукции;</t>
+  </si>
+  <si>
+    <t>Какой из ниже перечисленных прогнозных документов позволяет оценить ликвидность инвестиционного проекта? 3.3 :</t>
+  </si>
+  <si>
+    <t>прогнозный баланс;</t>
+  </si>
+  <si>
+    <t>прогноз прибылей и убытков;</t>
+  </si>
+  <si>
+    <t>кассовый план;</t>
+  </si>
+  <si>
+    <t>все три выше перечисленных документа</t>
+  </si>
+  <si>
+    <t>Вопрос 22
+Выполнен
+Баллов: 1,00 из 1,00
+Какой из ниже перечисленных прогнозных документов позволяет оценить ликвидность инвестиционного проекта? 3.3 :
+Выберите один ответ:
+a.
+прогнозный баланс;
+b.
+прогноз прибылей и убытков;
+c.
+кассовый план;
+d.
+все три выше перечисленных документа.</t>
+  </si>
+  <si>
+    <t>Как рассчитывается показатель «сила воздействия финансового рычага» в соответствии с американской концепцией? 8.16:</t>
+  </si>
+  <si>
+    <t>отношение изменения (в %) операционной прибыли (НРЭИ) к изменению (в %) чистой прибыли на акцию;</t>
+  </si>
+  <si>
+    <t>отношение маржинальной прибыли к операционной прибыли;</t>
+  </si>
+  <si>
+    <t>отношение операционной прибыли к прибыли к налогообложению</t>
+  </si>
+  <si>
+    <t>отношение изменения (в %) чистой прибыли на акцию к изменению (в %) операционной прибыли (НРЭИ);</t>
+  </si>
+  <si>
+    <t>Вопрос 23
+Выполнен
+Баллов: 0,00 из 1,00
+Как рассчитывается показатель «сила воздействия финансового рычага» в соответствии с американской концепцией?
+8.16:
+Выберите один ответ:
+a.
+отношение изменения (в %) операционной прибыли (НРЭИ) к изменению (в %) чистой прибыли на акцию;
+b.
+отношение маржинальной прибыли к операционной прибыли;
+c.
+отношение операционной прибыли к прибыли к налогообложению.
+d.
+отношение изменения (в %) чистой прибыли на акцию к изменению (в %) операционной прибыли (НРЭИ);</t>
+  </si>
+  <si>
+    <t>В каком из ниже приведенных случаев при операционном рычаге, равном 10, вместо операционной прибыли возникает убыток? 8.5:</t>
+  </si>
+  <si>
+    <t>выручка снижается на 1%</t>
+  </si>
+  <si>
+    <t>выручка снижается на 8%;</t>
+  </si>
+  <si>
+    <t>выручка снижается на 15%;</t>
+  </si>
+  <si>
+    <t>выручка снижается на 10%;</t>
+  </si>
+  <si>
+    <t>Вопрос 24
+Выполнен
+Баллов: 1,00 из 1,00
+В каком из ниже приведенных случаев при операционном рычаге, равном 10, вместо операционной прибыли возникает
+убыток? 8.5:
+Выберите один ответ:
+a.
+выручка снижается на 1%.
+b.
+выручка снижается на 8%;
+c.
+выручка снижается на 15%;
+d.
+выручка снижается на 10%;</t>
+  </si>
+  <si>
+    <t>Компания А эмитировала 10%-ные долговые обязательства. Чему равна стоимость этого источника средств, если налог на прибыль компании составляет 33%? 6.5:</t>
+  </si>
+  <si>
+    <t>6,7%</t>
+  </si>
+  <si>
+    <t>3,3%</t>
+  </si>
+  <si>
+    <t>Вопрос 25
+Выполнен
+Баллов: 1,00 из 1,00
+Компания А эмитировала 10%-ные долговые обязательства. Чему равна стоимость этого источника средств, если налог
+на прибыль компании составляет 33%? 6.5:
+Выберите один ответ:
+a.
+данных для расчета недостаточно
+b.
+6,7%
+c.
+3,3%</t>
+  </si>
+  <si>
+    <t>В результате реализации стратегии реструктуризации предприятие увеличило величину такого показателя как добавленная стоимость. Как это отразится на потребности в финансировании ее деятельности? 1.6:</t>
+  </si>
+  <si>
+    <t>в результате потребность в финансировании снизится, т.к. снизятся его издержки</t>
+  </si>
+  <si>
+    <t>отмеченный факт не связан с потребностью в финансировании деятельности предприятия;</t>
+  </si>
+  <si>
+    <t>в результате потребность в финансировании снизится, т.к. увеличится прибыль предприятия;</t>
+  </si>
+  <si>
+    <t>в результате потребность в финансировании возрастет, т.к. увеличится масштаб его деятельности;</t>
+  </si>
+  <si>
+    <t>Вопрос 26
+Выполнен
+Баллов: 0,00 из 1,00
+В результате реализации стратегии реструктуризации предприятие увеличило величину такого показателя как
+добавленная стоимость. Как это отразится на потребности в финансировании ее деятельности? 1.6:
+Выберите один ответ:
+a.
+в результате потребность в финансировании снизится, т.к. снизятся его издержки.
+b.
+отмеченный факт не связан с потребностью в финансировании деятельности предприятия;
+c.
+в результате потребность в финансировании снизится, т.к. увеличится прибыль предприятия;
+d.
+в результате потребность в финансировании возрастет, т.к. увеличится масштаб его деятельности;</t>
+  </si>
+  <si>
+    <t>Размер инвестиции составляет 200 000 тыс.руб. Запланированы следующие денежные потоки в результате реализации проекта: в первом году 50 000 тыс.руб.; во втором году 50 000 тыс.руб.; в третьем году 90000 тыс.руб.; в четвертом 110000 тыс.руб. Ставка дисконтирования равна 15%. Определить индекс доходности проекта (PI), округление до сотых. 4.6 :</t>
+  </si>
+  <si>
+    <t>1,55;</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,55;</t>
+  </si>
+  <si>
+    <t>1,05;</t>
+  </si>
+  <si>
+    <t>Вопрос 27
+Выполнен
+Баллов: 1,00 из 1,00
+Размер инвестиции составляет 200 000 тыс.руб. Запланированы следующие денежные потоки в результате реализации
+проекта: в первом году 50 000 тыс.руб.; во втором году 50 000 тыс.руб.; в третьем году 90000 тыс.руб.; в четвертом 110000
+тыс.руб. Ставка дисконтирования равна 15%. Определить индекс доходности проекта (PI), округление до сотых. 4.6 :
+Выберите один ответ:
+a.
+1,55;
+b.
+0,06.
+c.
+0,55;
+d.
+1,05;</t>
+  </si>
+  <si>
+    <t>Как повлияет на величину чистых активов предприятия начисление и выплата дивидендов акционерам? 1.8:</t>
+  </si>
+  <si>
+    <t>величина чистых активов Не изменится ни в случае начисления, ни в случае выплаты дивидендов:</t>
+  </si>
+  <si>
+    <t>величина чистых активов уменьшится в случае выплаты дивидендов</t>
+  </si>
+  <si>
+    <t>величина чистых активов изменится как в случае начисления, так и в случае выплаты дивидендов:</t>
+  </si>
+  <si>
+    <t>величина чистых активов уменьшится в случае начисления дивидендов:</t>
+  </si>
+  <si>
+    <t>Вопрос 28
+Выполнен
+Баллов: 1,00 из 1,00
+Как повлияет на величину чистых активов предприятия начисление и выплата дивидендов акционерам? 1.8:
+Выберите один ответ:
+a.
+величина чистых активов Не изменится ни в случае начисления, ни в случае выплаты дивидендов:
+b.
+величина чистых активов уменьшится в случае выплаты дивидендов.
+c.
+величина чистых активов изменится как в случае начисления, так и в случае выплаты дивидендов:
+d.
+величина чистых активов уменьшится в случае начисления дивидендов:</t>
+  </si>
+  <si>
+    <t>Какими бывают причины развития кризиса? 10.6:</t>
+  </si>
+  <si>
+    <t>объективными и субъективными</t>
+  </si>
+  <si>
+    <t>количественными и качественными;</t>
+  </si>
+  <si>
+    <t>обратимыми и необратимыми;</t>
+  </si>
+  <si>
+    <t>Вопрос 29
+Выполнен
+Баллов: 1,00 из 1,00
+Какими бывают причины развития кризиса? 10.6:
+Выберите один ответ:
+a.
+объективными и субъективными.
+b.
+количественными и качественными;
+c.
+обратимыми и необратимыми;</t>
+  </si>
+  <si>
+    <t>Какое решение необходимо принять для снижения риска инвестиционного портфеля? 5.3 :</t>
+  </si>
+  <si>
+    <t>объединение активов, доходности которых связаны обратной функциональной зависимостью,</t>
+  </si>
+  <si>
+    <t>объединение активов, доходности которых связаны прямой функциональной зависимостью,</t>
+  </si>
+  <si>
+    <t>Вопрос 30
+Выполнен
+Баллов: 1,00 из 1,00
+Какое решение необходимо принять для снижения риска инвестиционного портфеля? 5.3 :
+Выберите один ответ:
+a.
+объединение активов, доходности которых связаны обратной функциональной зависимостью,
+b.
+объединение активов, доходности которых связаны прямой функциональной зависимостью,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анализ денежных средств, проведенный косвенным методом, выявил, что денежный поток от основной деятельности предприятия имеет отрицательное значение. Как Вы оцениваете этот факт?  </t>
+  </si>
+  <si>
+    <t>a. это отрицательный факт, т.к. он свидетельствует о том, что основная деятельность предприятия предприятие генерирует недостаточный поток денежных средств</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. по этому факту нельзя сделать вывод о финансовом «здоровье» предприятия</t>
+  </si>
+  <si>
+    <t>c. это положительный факт в работе, т.к. он свидетельствует о том, что предприятие инвестирует свои средства в развитие</t>
+  </si>
+  <si>
+    <t>Финансовый учет и отчетность компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закончите предложение: «Балансовые остатки денежных средств увеличиваются в результате…»  </t>
+  </si>
+  <si>
+    <t>a. Увеличения капитала и резервов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Прироста остатков производственных запасов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. Прироста дебиторской задолженности </t>
+  </si>
+  <si>
+    <t>d. Снижения кредиторской задолженности</t>
+  </si>
+  <si>
+    <t>Что из перечисленного увеличит денежный поток от финансовой деятельности?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. выплата дивидендов акционерам </t>
+  </si>
+  <si>
+    <t>b. погашение краткосрочного банковского кредита</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. дополнительная эмиссия акций </t>
+  </si>
+  <si>
+    <t>d. предоставление предприятием долгосрочного займа дочерней компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данные из баланса компании N на конец года, тыс.руб., приведены в таблице. Статья баланса Значение Внеоборотные активы 1900 Дебиторская задолженность 365 Производственные запасы ? Денежные средства 5 Краткосрочная дебиторская задолженность 305 Резерв по сомнительным долгам 15 Чистый оборотный капитал 100 Уставный капитал 1500 Нераспределенная прибыль ? Актив 3000 Заполните недостающие значения статей баланса и рассчитайте коэффициент текущей ликвидности </t>
+  </si>
+  <si>
+    <t>a. Производственные запасы - 150, Нераспределенная прибыль - 500, Коэффициент текущей ликвидности 0,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. Производственные запасы - 440, Нераспределенная прибыль - 500, Коэффициент текущей ликвидности 1,1 </t>
+  </si>
+  <si>
+    <t>c. Производственные запасы - 150, Нераспределенная прибыль - 400, Коэффициент текущей ликвидности 0,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. Производственные запасы - 440, Нераспределенная прибыль - 500, Коэффициент текущей ликвидности 0,91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кредиторы используют финансовую отчетность преимущественно для того, чтобы </t>
+  </si>
+  <si>
+    <t>a оценить ликвидность, риски и прибыльность Компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Для заключения договоров найма </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. Для прогнозирования будущих дивидендов </t>
+  </si>
+  <si>
+    <t>Верно или неверно утверждение: «финансовая отчётность полезна сотрудникам для понимания стабильности фирмы и оценки способности компании выполнять условия трудовых договоров»</t>
+  </si>
+  <si>
+    <t>Верно</t>
+  </si>
+  <si>
+    <t>Неверно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cвойство активов быть быстро обращенными в платежные средства называется: </t>
+  </si>
+  <si>
+    <t>a. безубыточностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. рентабельностью </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. деловой активностью </t>
+  </si>
+  <si>
+    <t>d. ликвидностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Денежный поток – это</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Сумма денежных поступлений и выплат за определенный период времени </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Разность суммарных поступлений и выплат денежных средств за определенный период времени </t>
+  </si>
+  <si>
+    <t>c. Выплаты денежных средств за определенный период времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. Поступления денежных средств за определенный период времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Следующая информация взята из отчетов Jasper Inc. по состоянию на 31 января 2015 г. Статья Сумма, $ Статья Сумма, $ Денежные средства 1 000Кредиторская 17 000 задолженность поставщикам Оборудование 10 000Дебиторская 4 000 задолженность Нематериальные активы 5 000Запасы 15 000 Добавочный капитал 4 000Нераспределённая 3 500 прибыль Кредиты банков 15 000Задолженность перед 500 сотрудниками Уставный капитал ?Здания и сооружения 25 000 Требуется: Рассчитайте уставный капитал </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. $60 000 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. $20 000 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. $18 000 </t>
+  </si>
+  <si>
+    <t>d. $2 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Данные из баланса компании N на конец года, тыс.руб., приведены в таблице. Статья баланса Значение Внеоборотные активы 1900 Дебиторская задолженность 365 Производственные запасы ? Денежные средства 5 Краткосрочная дебиторская задолженность 305 Резерв по сомнительным долгам 15 Чистый оборотный капитал 100 Уставный капитал 1500 Нераспределенная прибыль ? Актив 3000 Заполните недостающие значения статей баланса </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. Производственные запасы - 150, Нераспределенная прибыль - 500, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Производственные запасы - 440, Нераспределенная прибыль - 500, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. Производственные запасы - 150, Нераспределенная прибыль - 400 </t>
+  </si>
+  <si>
+    <t>d. Производственные запасы - 440, Нераспределенная прибыль - 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Баланс предприятия на 1.04. 18 г. Актив Пассив Расчетный счет 89800 Кредиторская задолженность поставщикам 97000 Дебиторская задолженность задолженность 49000 Задолженность бюджету 28630 Товары на складе 129000 Уставный капитал 70000 Нераспределенная прибыль 72170 Итого: 267800 Итого: 267800 Как изменится баланс, если 2.04.18 г. планируется следующие операции: а) Погашение кредиторской задолженности поставщикам на 20%; б) Получение денег от дебитора А в размере  28200; в) выплата дивидендов акционерам в размере 10% от всей накопленной прибыли. В ответе предоставить баланс на 2.04.18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. 233966 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Валюта баланса не изменится </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. 241183 </t>
+  </si>
+  <si>
+    <t>d. В результате баланс станет дефицитным: актив  248400, пассив 241183</t>
+  </si>
+  <si>
+    <t>Что из перечисленного подразумевает косвенный метод анализа денежных потоков?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Факторный анализ прибыли</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. Составление отчета об изменении капитала</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. Составление отчета о движении денежных средств по счетам Главной книги</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. Составление отчета о движении денежных средств путем корректировки чистой прибыли</t>
+  </si>
+  <si>
+    <t>Начинается с чистой прибыли, которая затем корректируется на:
+амортизацию;
+изменение дебиторской задолженности;
+изменение запасов;
+изменение кредиторской задолженности;
+прочие неденежные статьи.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компания А взяла кредит в банке на сумму 5000 долларов. Требуется: указать, к какой категории относится каждая операция или корректировка в отчете о движении денежных средств: операционная (O), финансовая (F) или инвестиционная (I) деятельность. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. операционная (O) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. инвестиционная (I) </t>
+  </si>
+  <si>
+    <t>c. финансовая (F)</t>
+  </si>
+  <si>
+    <t>Компания А приобрела инвентарь на 50 000 долларов.  Выберите вариант отражения операция в Отчете о движении денежных средств (косвенным методом):</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Операционная деятельность: $50,000, отток денежных средств </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Инвестиционная деятельность: $50,000, отток денежных средств </t>
+  </si>
+  <si>
+    <t>c. Финансовая деятельность: $50,000, приток денежных средств</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. Финансовая деятельность: $50,000, отток денежных средств</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Покупка </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>инвентаря</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> обычно относится к приобретению имущества/основных средств или долгосрочных активов. Поэтому в отчёте о движении денежных средств такая операция отражается как:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Коэффициент абсолютной ликвидности показывает: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. какую часть текущих обязательств предприятие может погасить за счет поступлений по расчетам </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. какую часть текущих обязательств предприятие может погасить за счет продажи всех активов </t>
+  </si>
+  <si>
+    <t>c. какую часть текущих обязательств предприятие может погасить за счет денежных средств и финансовых вложений (т.е. немедленно)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. какую часть текущих обязательств предприятие может погасить реализовав все оборотные активы</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Коэффициент абсолютной ликвидности показывает, какая часть </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>краткосрочных обязательств</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> может быть погашена </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>сразу</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, за счёт наиболее ликвидных активов:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Коэффициент обеспеченности собственными оборотными средствами определяется как </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. отношение собственных оборотных средств к выручке от продаж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. отношение собственных оборотных средств к оборотным активам </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. отношение собственных оборотных средств к чистой прибыли </t>
+  </si>
+  <si>
+    <t>d. отношение собственных оборотных средств к валюте баланса</t>
+  </si>
+  <si>
+    <t>Коэффициент обеспеченности собственными оборотными средствами показывает, какая часть оборотных активов профинансирована за счёт собственных источников.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К ускорению оборачиваемости оборотного капитала приводит: </t>
+  </si>
+  <si>
+    <t>a. сокращение  сроков погашения платежей</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. увеличение оборотного капитала</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. увеличение сроков погашения платежей </t>
+  </si>
+  <si>
+    <t>d. сокращение выручки от продаж</t>
+  </si>
+  <si>
+    <t>Ускорение оборачиваемости оборотного капитала означает, что деньги быстрее возвращаются в оборот компании.
+Сокращение сроков погашения платежей, например дебиторской задолженности, приводит к тому, что предприятие быстрее получает деньги от покупателей и может снова использовать их в деятельности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">О чем свидетельствует случай, когда темпы роста прибыли выше темпов роста выручки? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. снижении рентабельности продаж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. о повышении рентабельности активов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. снижении фондоотдачи </t>
+  </si>
+  <si>
+    <t>d. повышении рентабельности продаж</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Если </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>прибыль растёт быстрее, чем выручка</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, значит с каждого рубля продаж компания получает больше прибыли.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Компания покупает оборудование за наличный расчет. На каком из следующих балансовых счетов компания должна отразить это оборудование? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. Внеоборотные активы. Нематериальные активы </t>
+  </si>
+  <si>
+    <t>b. Внеоборотные активы. Основные средства</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. Оборотные активы. Запасы </t>
+  </si>
+  <si>
+    <t>При расчете денежного потока косвенным способом исходным элементом является. a. выручка от реализации b. себестоимость реализованной продукции c. валюта баланса d. чистая прибыль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. выручка от реализации </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. себестоимость реализованной продукции </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. валюта баланса </t>
+  </si>
+  <si>
+    <t>d. чистая прибыль</t>
+  </si>
+  <si>
+    <t>При косвенном методе расчёта денежного потока исходным показателем является чистая прибыль.
+Далее она корректируется на:
+неденежные расходы, например амортизацию;
+изменения оборотного капитала;
+изменения дебиторской и кредиторской задолженности;
+изменения запасов.</t>
+  </si>
+  <si>
+    <t>Чем выше норма добавленной стоимости, тем у предприятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. не достаточно данных для ответа на вопрос</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. этот показатель не связан с уровнем финансирования текущей деятельности</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. меньше потребность в финансировании текущей деятельности </t>
+  </si>
+  <si>
+    <t>d. больше потребность в финансировании текущей деятельности</t>
+  </si>
+  <si>
+    <t>Чем выше норма добавленной стоимости, тем большая часть стоимости создаётся внутри предприятия. Это обычно означает, что компания несёт больше собственных затрат на производство, оплату труда, содержание процессов и ресурсов.
+Следовательно, ей требуется больше средств для поддержания текущей деятельности, то есть возрастает потребность в финансировании оборотного капитала.</t>
+  </si>
+  <si>
+    <t>Компания закупает материалы у своего поставщика в этом месяце и заплатит поставщику в следующем месяце. В каком из следующих балансовых счетов компания должна отразить обязательство по оплате своему поставщику?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Кредиторская задолженность</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. Дебиторская задолженност</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ь c. Кредиты и займы </t>
+  </si>
+  <si>
+    <t>d. Основные средства</t>
+  </si>
+  <si>
+    <t>Компания выпустила облигации  на сумму 50 000 000 руб. Требуется: указать, к какой категории относится каждая операция или корректировка в отчете о движении денежных средств: операционная (O), финансовая (F) или инвестиционная (I) деятельность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. операционная (O) </t>
+  </si>
+  <si>
+    <t>b. финансовая (F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. инвестиционная (I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Отчет о финансовом результате  содержит информацию о </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. Доходах и расходах </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. Активах и обязательствах </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. Активах и амортизации </t>
+  </si>
+  <si>
+    <t>d. Активах и расходах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Показатель дебиторской задолженности, характеризующий скорость превращения в денежные средства, называется </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. оборачиваемость </t>
+  </si>
+  <si>
+    <t>b. платежеспособность</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. рентабельность</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> d. устойчивость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закончите предложение: «Балансовые остатки денежных средств увеличиваются в результате…» </t>
+  </si>
+  <si>
+    <t>a. Прироста дебиторской задолженности</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b. Снижения кредиторской задолженности</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c. Увеличения капитала и резервов </t>
+  </si>
+  <si>
+    <t>d. Прироста остатков производственных запасов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отчет о финансовом результате показывает </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. финансовое состояние предприятие на определенный момент времени </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. результат деятельности предприятия за определённый период времени льтат деятельности предприятия за определённый период времени </t>
+  </si>
+  <si>
+    <t>c. источники денежных средств и их использование за определённый период времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При росте величины чистого оборотного капитала </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. степень риска ликвидности уменьшается, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. верного ответа нет </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. степень риска потери ликвидности увеличивается, </t>
+  </si>
+  <si>
+    <t>d. риск ликвидности не изменяется,</t>
+  </si>
+  <si>
+    <t>Если величина чистого оборотного капитала растёт, значит у предприятия становится больше оборотных активов, покрывающих краткосрочные обязательства.</t>
+  </si>
+  <si>
+    <t>Примером реализации контрольной функции финансов является</t>
+  </si>
+  <si>
+    <t>передача сдачи в магазине</t>
+  </si>
+  <si>
+    <t>формирование расходных статей государственного бюджета</t>
+  </si>
+  <si>
+    <t>расчет отклонения фактических расходов от плановых</t>
+  </si>
+  <si>
+    <t>Выберите НЕ ВЕРНОЕ утверждение</t>
+  </si>
+  <si>
+    <t>активный капитал состоит из двух частей: основного капитала и оборотного капитала </t>
+  </si>
+  <si>
+    <t>основной капитал характеризуется длительным характером использования</t>
+  </si>
+  <si>
+    <t>Выберете правильное расположение от самого широкого понятия к самому узкому понятию</t>
+  </si>
+  <si>
+    <t>экономика-денежные отношения-финансы</t>
+  </si>
+  <si>
+    <t>экономика-финансы-денежные отношения</t>
+  </si>
+  <si>
+    <t>денежные отношения-экономика-финансы</t>
+  </si>
+  <si>
+    <t>финансы-экономика-денежные отношения</t>
+  </si>
+  <si>
+    <t>Бизнес-модель компании – это</t>
+  </si>
+  <si>
+    <t>это часть стратегии бизнеса, описывающая принципы, способы и правила ведения бизнеса
+организацией</t>
+  </si>
+  <si>
+    <t>показывать максимально точные аналитические данные по различным ситуациям, которые так или иначе влияют на дальнейшее принятие управленческих решений.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Стратегия компании – это?</t>
+  </si>
+  <si>
+    <t>план действий на долгосрочный период (на год или несколько лет),
+которого придерживается компания для достижения своих целей</t>
+  </si>
+  <si>
+    <t>Финансовая модель это</t>
+  </si>
+  <si>
+    <t>схема, показывающая экономическое состояние объекта или его элементы как по компании в целом, так и отдельно по отделам.</t>
+  </si>
+  <si>
+    <t>Какие инструменты кроме электронных таблиц могут использоваться?</t>
+  </si>
+  <si>
+    <t>1с</t>
+  </si>
+  <si>
+    <t>На каком этапе разработки фин. Модели происходит оценка качества работоспособности модели в реальных условиях?</t>
+  </si>
+  <si>
+    <t>Тестирования</t>
+  </si>
+  <si>
+    <t>Чем больше влияние неопределенности, тем период фин. планирования должен быть?</t>
+  </si>
+  <si>
+    <t>длинее</t>
+  </si>
+  <si>
+    <t>короче</t>
+  </si>
+  <si>
+    <t>не влияет</t>
+  </si>
+  <si>
+    <t>недостаточно данных для ответа</t>
+  </si>
+  <si>
+    <t>Рентабельность собственного капитала 10%, ставка по кредиту 15%, выгодно ли предприятию взять кредит?</t>
+  </si>
+  <si>
+    <t>Нет, не выгодно</t>
+  </si>
+  <si>
+    <t>Да, выгодно</t>
+  </si>
+  <si>
+    <t>Не хватает данных</t>
+  </si>
+  <si>
+    <t>Не влияет</t>
+  </si>
+  <si>
+    <t>Выделите преимущественно переменные затраты</t>
+  </si>
+  <si>
+    <t>Сырье, упаковка, зарплата рабочего персонала</t>
+  </si>
+  <si>
+    <t>Опережающий рост выручки по сравнению с ростом оборотных активов свидетельствует о</t>
+  </si>
+  <si>
+    <t>Что является главным результатом деятельности компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка  </t>
+  </si>
+  <si>
+    <t>Какие цели моделирования в формировании NPV</t>
+  </si>
+  <si>
+    <t>Финансирование инвестиционных проектов за счет доходов, которые несет предприятие
+называется</t>
+  </si>
+  <si>
+    <t>Предприятие взяло кредит 10000 под 10% процентную ставку на 2 года. Проценты сотавят ?</t>
+  </si>
+  <si>
+    <t>Куда попадет денежный поток от продажи ненужного оборудования</t>
+  </si>
+  <si>
+    <t>Операционный</t>
+  </si>
+  <si>
+    <t>Инвестиционный</t>
+  </si>
+  <si>
+    <t>Финанансовый</t>
+  </si>
+  <si>
+    <t>никуда</t>
+  </si>
+  <si>
+    <t>Как исчисляется налоговая база с целью исчисления налога на прибыль</t>
+  </si>
+  <si>
+    <t>Доходы-расходы</t>
+  </si>
+  <si>
+    <t>Срок оплаты НДС</t>
+  </si>
+  <si>
+    <t>Не позднее 28-го числа каждого из 3 месяцев, следующих за отчетным кварталом</t>
+  </si>
+  <si>
+    <t>Объектом налогообложения по налогу на имущество является</t>
+  </si>
+  <si>
+    <t>Здания, офисы, склады</t>
+  </si>
+  <si>
+    <t>Куплено сырье, ставка НДС … какая ставка НДС принята к учету?</t>
+  </si>
+  <si>
+    <t>это система бухгалтерского учета, отражающая движение денежных средств компании за отчетный период</t>
+  </si>
+  <si>
+    <t>это организационная структура предприятия, определяющая подчиненность сотрудников и распределение должностных обязанностей</t>
+  </si>
+  <si>
+    <t>это краткосрочный план продаж, устанавливающий объем реализации продукции на ближайший месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Финансовое моделирование и налоговое планирование </t>
+  </si>
+  <si>
+    <t>это документ, описывающий только производственные процессы предприятия без учета доходов и расходов</t>
+  </si>
+  <si>
+    <t>это перечень должностных обязанностей сотрудников, определяющий порядок взаимодействия между отделами</t>
+  </si>
+  <si>
+    <t>это маркетинговая схема, показывающая способы продвижения товаров и привлечения покупателей</t>
+  </si>
+  <si>
+    <t>определять только размер прибыли компании за прошлый период без анализа причин ее изменения</t>
+  </si>
+  <si>
+    <t>формировать рекламную стратегию предприятия и выбирать наиболее эффективные каналы продвижения</t>
+  </si>
+  <si>
+    <t>набор правил внутреннего распорядка, регулирующий поведение сотрудников на рабочем месте</t>
+  </si>
+  <si>
+    <t>схема текущего распределения ресурсов между подразделениями без учета долгосрочных целей компании</t>
+  </si>
+  <si>
+    <t>краткосрочный финансовый отчет, отражающий доходы и расходы компании за один месяц</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>Power Poin</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>Сбор данных</t>
+  </si>
+  <si>
+    <t>Утверждения</t>
+  </si>
+  <si>
+    <t>Разработка</t>
+  </si>
+  <si>
+    <t>аренда помещения, амортизация оборудования, оклад административного персонала</t>
+  </si>
+  <si>
+    <t>проценты по кредиту, налог на имущество, расходы на охрану офиса</t>
+  </si>
+  <si>
+    <t>расходы на рекламу, обучение сотрудников, покупка офисной мебели</t>
+  </si>
+  <si>
+    <t>ускорении оборачиваемости и повышению эффективности использования</t>
+  </si>
+  <si>
+    <t>снижению оборачиваемости активов и увеличению потребности компании в дополнительном финансировании</t>
+  </si>
+  <si>
+    <t>росту постоянных затрат и уменьшению эффективности использования ресурсов предприятия</t>
+  </si>
+  <si>
+    <t>сокращению объема продаж и снижению финансовой устойчивости компании</t>
+  </si>
+  <si>
+    <t>Активы</t>
+  </si>
+  <si>
+    <t>Затраты</t>
+  </si>
+  <si>
+    <t>определение общего размера выручки проекта без учета вложений и будущих затрат</t>
+  </si>
+  <si>
+    <t>расчет количества сотрудников, необходимых для реализации инвестиционного проекта</t>
+  </si>
+  <si>
+    <t>выбор организационной структуры предприятия для управления проектной деятельностью</t>
+  </si>
+  <si>
+    <t>Определение прибыльности проекта с учетом временой стоимости денег</t>
+  </si>
+  <si>
+    <t>кредитование</t>
+  </si>
+  <si>
+    <t>субсидирование</t>
+  </si>
+  <si>
+    <t>амортизация</t>
+  </si>
+  <si>
+    <t>реинвестирование</t>
+  </si>
+  <si>
+    <t>доходы + расходы</t>
+  </si>
+  <si>
+    <t>активы − обязательства</t>
+  </si>
+  <si>
+    <t>выручка − себестоимость продаж без учета прочих расходов</t>
+  </si>
+  <si>
+    <t>Не позднее 28-го числа каждого месяца, следующих за отчетным</t>
+  </si>
+  <si>
+    <t>единовременно не позднее 31 декабря текущего налогового периода</t>
+  </si>
+  <si>
+    <t>Не позднее 1-го числа каждого из 3 месяцев, следующих за отчетным кварталом</t>
+  </si>
+  <si>
+    <t>товары, сырье и материалы, находящиеся на складе предприятия</t>
+  </si>
+  <si>
+    <t>транспортные средства, используемые только для личных нужд сотрудников</t>
+  </si>
+  <si>
+    <t>денежные средства на расчетных счетах организации</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -985,6 +3514,40 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D0710"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D0710"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF373A3C"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D0710"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1012,13 +3575,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1322,12 +3909,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L31"/>
+  <sheetPr codeName="Лист1"/>
+  <dimension ref="A1:L189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="7" width="32" customWidth="1"/>
+    <col min="2" max="2" width="45" style="3" customWidth="1"/>
+    <col min="3" max="6" width="32" style="3" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
@@ -2379,6 +4968,4617 @@
         <v>18</v>
       </c>
     </row>
+    <row r="32" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="99" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="H63" t="s">
+        <v>182</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="66" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" ht="66" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="F83" s="6"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" ht="90" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="195" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="75" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="180" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="165" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="225" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="165" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="105" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J98" t="s">
+        <v>691</v>
+      </c>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="75" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J99" t="s">
+        <v>697</v>
+      </c>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="120" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="240" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J102" t="s">
+        <v>715</v>
+      </c>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="240" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="270" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="90" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="105" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="75" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="120" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="90.75" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="90.75" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="D116" t="s">
+        <v>830</v>
+      </c>
+      <c r="E116" t="s">
+        <v>829</v>
+      </c>
+      <c r="F116" t="s">
+        <v>831</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="D117" t="s">
+        <v>832</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="60.75" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>118</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C121" t="s">
+        <v>839</v>
+      </c>
+      <c r="D121" t="s">
+        <v>838</v>
+      </c>
+      <c r="E121" t="s">
+        <v>840</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>801</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D122" t="s">
+        <v>842</v>
+      </c>
+      <c r="E122" t="s">
+        <v>843</v>
+      </c>
+      <c r="F122" t="s">
+        <v>844</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>122</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="60.75" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="C125" t="s">
+        <v>851</v>
+      </c>
+      <c r="D125" t="s">
+        <v>852</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="F125" t="s">
+        <v>853</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="C126" s="3">
+        <v>13310</v>
+      </c>
+      <c r="D126" s="3">
+        <v>3310</v>
+      </c>
+      <c r="E126" s="3">
+        <v>8524</v>
+      </c>
+      <c r="F126" s="3">
+        <v>7893</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C128" t="s">
+        <v>857</v>
+      </c>
+      <c r="D128" t="s">
+        <v>855</v>
+      </c>
+      <c r="E128" t="s">
+        <v>856</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>815</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E129" t="s">
+        <v>859</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D130" t="s">
+        <v>861</v>
+      </c>
+      <c r="E130" t="s">
+        <v>862</v>
+      </c>
+      <c r="F130" t="s">
+        <v>863</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="C131" s="3">
+        <v>22</v>
+      </c>
+      <c r="D131" s="3">
+        <v>10</v>
+      </c>
+      <c r="E131" s="3">
+        <v>18</v>
+      </c>
+      <c r="F131" s="3">
+        <v>20</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C132" s="3">
+        <v>32000</v>
+      </c>
+      <c r="D132" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E132" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F132" s="3">
+        <v>30000</v>
+      </c>
+      <c r="H132" t="s">
+        <v>183</v>
+      </c>
+      <c r="I132" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>132</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H133" t="s">
+        <v>182</v>
+      </c>
+      <c r="I133" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C134" s="3">
+        <v>30000</v>
+      </c>
+      <c r="D134" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E134" s="3">
+        <v>65200</v>
+      </c>
+      <c r="F134" s="3">
+        <v>31200</v>
+      </c>
+      <c r="H134" t="s">
+        <v>183</v>
+      </c>
+      <c r="I134" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>134</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C135" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="D135" s="3">
+        <v>24.2</v>
+      </c>
+      <c r="E135" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="H135" t="s">
+        <v>181</v>
+      </c>
+      <c r="I135" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C136" s="3">
+        <v>1900</v>
+      </c>
+      <c r="D136" s="3">
+        <v>7410</v>
+      </c>
+      <c r="E136" s="3">
+        <v>18210</v>
+      </c>
+      <c r="H136" t="s">
+        <v>181</v>
+      </c>
+      <c r="I136" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>136</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H137" t="s">
+        <v>182</v>
+      </c>
+      <c r="I137" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>137</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H138" t="s">
+        <v>182</v>
+      </c>
+      <c r="I138" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>138</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C139" s="11">
+        <v>119000</v>
+      </c>
+      <c r="D139" s="3">
+        <v>116098</v>
+      </c>
+      <c r="E139" s="3">
+        <v>123000</v>
+      </c>
+      <c r="F139" s="3">
+        <v>120000</v>
+      </c>
+      <c r="H139" t="s">
+        <v>182</v>
+      </c>
+      <c r="I139" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>139</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H140" t="s">
+        <v>183</v>
+      </c>
+      <c r="I140" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C141" s="3">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="D141" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="E141" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="F141" s="3">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="H141" t="s">
+        <v>181</v>
+      </c>
+      <c r="I141" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C142" s="3">
+        <v>388</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E142" s="3">
+        <v>155200</v>
+      </c>
+      <c r="F142" s="3">
+        <v>174600</v>
+      </c>
+      <c r="H142" t="s">
+        <v>182</v>
+      </c>
+      <c r="I142" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C143" s="3">
+        <v>23175</v>
+      </c>
+      <c r="D143" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E143" s="3">
+        <v>13590</v>
+      </c>
+      <c r="F143" s="3">
+        <v>27900</v>
+      </c>
+      <c r="H143" t="s">
+        <v>183</v>
+      </c>
+      <c r="I143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C144" s="3">
+        <v>216850</v>
+      </c>
+      <c r="D144" s="3">
+        <v>380</v>
+      </c>
+      <c r="E144" s="3">
+        <v>188</v>
+      </c>
+      <c r="F144" s="3">
+        <v>182553</v>
+      </c>
+      <c r="H144" t="s">
+        <v>181</v>
+      </c>
+      <c r="I144" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H145" t="s">
+        <v>180</v>
+      </c>
+      <c r="I145" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C146" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D146" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E146" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="F146" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="H146" t="s">
+        <v>182</v>
+      </c>
+      <c r="I146" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>146</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C147" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D147" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E147" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F147" s="3">
+        <v>250000</v>
+      </c>
+      <c r="H147" t="s">
+        <v>181</v>
+      </c>
+      <c r="I147" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C148" s="3">
+        <v>25</v>
+      </c>
+      <c r="D148" s="3">
+        <v>37</v>
+      </c>
+      <c r="E148" s="3">
+        <v>30</v>
+      </c>
+      <c r="F148" s="3">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
+        <v>180</v>
+      </c>
+      <c r="I148" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C149" s="3">
+        <v>10</v>
+      </c>
+      <c r="D149" s="3">
+        <v>120</v>
+      </c>
+      <c r="E149" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="F149" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H149" t="s">
+        <v>180</v>
+      </c>
+      <c r="I149" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C150" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="D150" s="3">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="E150" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="F150" s="3">
+        <v>7.65</v>
+      </c>
+      <c r="H150" t="s">
+        <v>183</v>
+      </c>
+      <c r="I150" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C151" s="3">
+        <v>309060</v>
+      </c>
+      <c r="D151" s="3">
+        <v>131940</v>
+      </c>
+      <c r="E151" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F151" s="3">
+        <v>490000</v>
+      </c>
+      <c r="H151" t="s">
+        <v>181</v>
+      </c>
+      <c r="I151" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G152" t="s">
+        <v>237</v>
+      </c>
+      <c r="H152" t="s">
+        <v>180</v>
+      </c>
+      <c r="I152" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H153" t="s">
+        <v>183</v>
+      </c>
+      <c r="I153" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H154" t="s">
+        <v>183</v>
+      </c>
+      <c r="I154" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H155" t="s">
+        <v>182</v>
+      </c>
+      <c r="I155" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H156" t="s">
+        <v>182</v>
+      </c>
+      <c r="I156" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H157" t="s">
+        <v>180</v>
+      </c>
+      <c r="I157" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H158" t="s">
+        <v>180</v>
+      </c>
+      <c r="I158" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G159" t="s">
+        <v>271</v>
+      </c>
+      <c r="H159" t="s">
+        <v>183</v>
+      </c>
+      <c r="I159" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G160" t="s">
+        <v>277</v>
+      </c>
+      <c r="H160" t="s">
+        <v>181</v>
+      </c>
+      <c r="I160" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G161" t="s">
+        <v>283</v>
+      </c>
+      <c r="H161" t="s">
+        <v>182</v>
+      </c>
+      <c r="I161" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H162" t="s">
+        <v>180</v>
+      </c>
+      <c r="I162" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I163" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I164" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I165" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I166" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I167" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I168" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I169" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="I170" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I171" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I172" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I173" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I174" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I175" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="150.75" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C176" s="3">
+        <v>126</v>
+      </c>
+      <c r="D176" s="3">
+        <v>124</v>
+      </c>
+      <c r="E176" s="3">
+        <v>60</v>
+      </c>
+      <c r="F176" s="3">
+        <v>64</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I176" t="s">
+        <v>335</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="210.75" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C177" s="3">
+        <v>728</v>
+      </c>
+      <c r="D177" s="3">
+        <v>122</v>
+      </c>
+      <c r="E177" s="3">
+        <v>850</v>
+      </c>
+      <c r="F177" s="3">
+        <v>679</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I177" t="s">
+        <v>335</v>
+      </c>
+      <c r="J177" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="195.75" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C178" s="3">
+        <v>2400</v>
+      </c>
+      <c r="D178" s="3">
+        <v>1250</v>
+      </c>
+      <c r="E178" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F178" s="3">
+        <v>-1450</v>
+      </c>
+      <c r="G178">
+        <v>540</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I178" t="s">
+        <v>335</v>
+      </c>
+      <c r="J178" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="240.75" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>178</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C179" s="3">
+        <v>4000</v>
+      </c>
+      <c r="D179" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E179" s="3">
+        <v>1950</v>
+      </c>
+      <c r="F179" s="3">
+        <v>1050</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I179" t="s">
+        <v>335</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="105.75" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C180" s="3">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D180" s="3">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E180" s="3">
+        <v>15</v>
+      </c>
+      <c r="F180" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I180" t="s">
+        <v>335</v>
+      </c>
+      <c r="J180" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <v>180</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C181" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D181" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E181" s="3">
+        <v>1</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I181" t="s">
+        <v>335</v>
+      </c>
+      <c r="J181" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="195.75" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I182" t="s">
+        <v>335</v>
+      </c>
+      <c r="J182" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="225.75" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C183" s="3">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="D183" s="3">
+        <v>17.54</v>
+      </c>
+      <c r="E183" s="3">
+        <v>17.375</v>
+      </c>
+      <c r="F183" s="3">
+        <v>11.74</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I183" t="s">
+        <v>335</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="165.75" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C184" s="3">
+        <v>76</v>
+      </c>
+      <c r="D184" s="3">
+        <v>78</v>
+      </c>
+      <c r="E184" s="3">
+        <v>87</v>
+      </c>
+      <c r="F184" s="3">
+        <v>85</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I184" t="s">
+        <v>335</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="150.75" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C185" s="3">
+        <v>6</v>
+      </c>
+      <c r="D185" s="3">
+        <v>3</v>
+      </c>
+      <c r="E185" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F185" s="3">
+        <v>7</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I185" t="s">
+        <v>335</v>
+      </c>
+      <c r="J185" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="150.75" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C186" s="3">
+        <v>175.5</v>
+      </c>
+      <c r="D186" s="3">
+        <v>184.5</v>
+      </c>
+      <c r="E186" s="3">
+        <v>199.4</v>
+      </c>
+      <c r="F186" s="3">
+        <v>196.6</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I186" t="s">
+        <v>335</v>
+      </c>
+      <c r="J186" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="180.75" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C187" s="3">
+        <v>150384</v>
+      </c>
+      <c r="D187" s="3">
+        <v>135483</v>
+      </c>
+      <c r="E187" s="3">
+        <v>125791</v>
+      </c>
+      <c r="F187" s="3">
+        <v>16514</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I187" t="s">
+        <v>335</v>
+      </c>
+      <c r="J187" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="120.75" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C188" s="3">
+        <v>7.6</v>
+      </c>
+      <c r="D188" s="3">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E188" s="3">
+        <v>179.24</v>
+      </c>
+      <c r="F188" s="3">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I188" t="s">
+        <v>335</v>
+      </c>
+      <c r="J188" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="180.75" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C189" s="3">
+        <v>120.5</v>
+      </c>
+      <c r="D189" s="3">
+        <v>119</v>
+      </c>
+      <c r="E189" s="3">
+        <v>123</v>
+      </c>
+      <c r="F189" s="3">
+        <v>135</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I189" t="s">
+        <v>335</v>
+      </c>
+      <c r="J189" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/STFM.xlsx
+++ b/data/STFM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\klimk\Documents\Gosy\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{858DF287-6D00-4E62-AB46-F878D09E63B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8A5DC1-5E10-48C6-898F-F0A9351B0AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2400" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,11 +19,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Вопросы!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="871">
   <si>
     <t>Номер вопроса</t>
   </si>
@@ -3495,6 +3506,47 @@
   </si>
   <si>
     <t>денежные средства на расчетных счетах организации</t>
+  </si>
+  <si>
+    <t>Выручка:
+1000×13000=13000000 руб.
+Удельная маржинальная прибыль:
+13000−7000=6000 руб.
+Точка безубыточности в натуральном выражении:
+Q
+безуб
+	​
+=
+6000
+2400000
+	​
+=400 шт.
+Запас финансовой прочности:
+ЗФП=
+1000
+1000−400
+	​
+×100%=60%
+✅ Запас финансовой прочности = 60 %.</t>
+  </si>
+  <si>
+    <t>Какой вид анализа позволяет оценить влияние некоторого параметра модели на результат?</t>
+  </si>
+  <si>
+    <t>Финансовый</t>
+  </si>
+  <si>
+    <t>Когортный</t>
+  </si>
+  <si>
+    <t>Чувствительности</t>
+  </si>
+  <si>
+    <t>Выручка 100 м. р., периоды оборота запасов 30 дней, ДЗ 40 дней, КЗ 35 дней. Найдите прирост оборотного капитала, если выручка увеличится на 15 проц..</t>
+  </si>
+  <si>
+    <t>Период оборота = Запас (Кз, Дз)/Выр * 360
+ФЦ = 30+40-35 = 35 , потом (35*15)/360 = 1,46</t>
   </si>
 </sst>
 </file>
@@ -3910,7 +3962,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6452,7 +6504,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -6478,7 +6530,9 @@
       <c r="I79" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="J79" s="2"/>
+      <c r="J79" s="2" t="s">
+        <v>864</v>
+      </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2" t="s">
         <v>416</v>
@@ -8799,11 +8853,11 @@
       <c r="E161" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" t="s">
+        <v>283</v>
+      </c>
+      <c r="G161" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="G161" t="s">
-        <v>283</v>
       </c>
       <c r="H161" t="s">
         <v>182</v>
@@ -9219,7 +9273,7 @@
         <v>679</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I177" t="s">
         <v>335</v>
@@ -9471,19 +9525,19 @@
         <v>360</v>
       </c>
       <c r="C186" s="3">
-        <v>175.5</v>
+        <v>96.6</v>
       </c>
       <c r="D186" s="3">
         <v>184.5</v>
       </c>
       <c r="E186" s="3">
-        <v>199.4</v>
+        <v>100</v>
       </c>
       <c r="F186" s="3">
         <v>196.6</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I186" t="s">
         <v>335</v>
@@ -9577,6 +9631,61 @@
       </c>
       <c r="J189" s="3" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I190" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="60.75" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C191" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="D191" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="E191" s="3">
+        <v>15</v>
+      </c>
+      <c r="F191" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I191" t="s">
+        <v>335</v>
+      </c>
+      <c r="J191" s="3" t="s">
+        <v>870</v>
       </c>
     </row>
   </sheetData>
